--- a/analise_eua/energia_eletrica/nrg/nrg_10q.xlsx
+++ b/analise_eua/energia_eletrica/nrg/nrg_10q.xlsx
@@ -433,65 +433,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T45"/>
+  <dimension ref="A1:U45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -502,60 +505,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>162</v>
+      </c>
+      <c r="C2" t="n">
         <v>178</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>732</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>180</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>693</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>1104</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>376</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>278</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>401</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>422</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>407</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>333</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>580</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>387</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>259</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>361</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>501</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>697</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>418</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>759</v>
       </c>
     </row>
@@ -566,60 +572,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>167</v>
+      </c>
+      <c r="C3" t="n">
         <v>176</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>323</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>446</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>730</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>12</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>688</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>241</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>263</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>365</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>330</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>3134</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>3970</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>2570</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>1748</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>533</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>55</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>15</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>36</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>51</v>
       </c>
     </row>
@@ -630,62 +639,65 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>50</v>
+      </c>
+      <c r="C4" t="n">
         <v>57</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>30</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>17</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>15</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>10</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>16</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>15</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>11</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>26</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>32</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>46</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>44</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>39</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>14</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>15</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>18</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>6</v>
-      </c>
-      <c r="S4" t="n">
-        <v>8</v>
       </c>
       <c r="T4" t="n">
         <v>8</v>
       </c>
+      <c r="U4" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -694,60 +706,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>3534</v>
+      </c>
+      <c r="C5" t="n">
         <v>3777</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>3332</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>3421</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>3512</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>3258</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>3402</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>3325</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>3764</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>3274</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>3519</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>4061</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>3862</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>3291</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>3096</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>2822</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>3037</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>1126</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>1015</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>915</v>
       </c>
     </row>
@@ -758,60 +773,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>793</v>
+      </c>
+      <c r="C6" t="n">
         <v>665</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>452</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>451</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>373</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>540</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>623</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>581</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>630</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>686</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>722</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>772</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>604</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>354</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>445</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>365</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>316</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>330</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>388</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>372</v>
       </c>
     </row>
@@ -822,60 +840,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>3188</v>
+      </c>
+      <c r="C7" t="n">
         <v>3081</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1928</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>2332</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>3436</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>2456</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>3520</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>3807</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>3710</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>4423</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>4400</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>9938</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>11323</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>9089</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>8528</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3975</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>1816</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>578</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>791</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>884</v>
       </c>
     </row>
@@ -886,60 +907,63 @@
         </is>
       </c>
       <c r="B8" t="n">
+        <v>441</v>
+      </c>
+      <c r="C8" t="n">
         <v>606</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>358</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>361</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
         <v>217</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>449</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>384</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>309</v>
       </c>
-      <c r="I8" t="n">
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="J8" t="n">
+      <c r="K8" t="n">
         <v>270</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>293</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>262</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>295</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>9</v>
       </c>
-      <c r="O8" t="n">
+      <c r="P8" t="n">
         <v>21</v>
       </c>
-      <c r="P8" t="n">
+      <c r="Q8" t="n">
         <v>80</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="R8" t="n">
         <v>298</v>
       </c>
-      <c r="R8" t="n">
+      <c r="S8" t="n">
         <v>77</v>
       </c>
-      <c r="S8" t="n">
+      <c r="T8" t="n">
         <v>136</v>
       </c>
-      <c r="T8" t="n">
+      <c r="U8" t="n">
         <v>200</v>
       </c>
     </row>
@@ -950,60 +974,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>1318</v>
+      </c>
+      <c r="C9" t="n">
         <v>1382</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>969</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>987</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
         <v>899</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>782</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>797</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>712</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>601</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>580</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>505</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>417</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>470</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>409</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>461</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>473</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>511</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>258</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>284</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>290</v>
       </c>
     </row>
@@ -1014,60 +1041,63 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>9653</v>
+      </c>
+      <c r="C10" t="n">
         <v>9922</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>8124</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>8195</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>9875</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>8611</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>9806</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>9268</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>9468</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>10121</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>10208</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>18963</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>21148</v>
       </c>
-      <c r="N10" t="n">
+      <c r="O10" t="n">
         <v>16837</v>
       </c>
-      <c r="O10" t="n">
+      <c r="P10" t="n">
         <v>14572</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>8624</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>6552</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>3087</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>3076</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>3479</v>
       </c>
     </row>
@@ -1078,60 +1108,63 @@
         </is>
       </c>
       <c r="B11" t="n">
+        <v>14076</v>
+      </c>
+      <c r="C11" t="n">
         <v>13533</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>3396</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>3192</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
         <v>2223</v>
       </c>
-      <c r="F11" t="n">
+      <c r="G11" t="n">
         <v>1818</v>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>1790</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>1768</v>
       </c>
-      <c r="I11" t="n">
+      <c r="J11" t="n">
         <v>1779</v>
       </c>
-      <c r="J11" t="n">
+      <c r="K11" t="n">
         <v>1706</v>
       </c>
-      <c r="K11" t="n">
+      <c r="L11" t="n">
         <v>1835</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1598</v>
       </c>
       <c r="M11" t="n">
         <v>1598</v>
       </c>
       <c r="N11" t="n">
+        <v>1598</v>
+      </c>
+      <c r="O11" t="n">
         <v>1643</v>
       </c>
-      <c r="O11" t="n">
+      <c r="P11" t="n">
         <v>1976</v>
       </c>
-      <c r="P11" t="n">
+      <c r="Q11" t="n">
         <v>2016</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
         <v>2328</v>
       </c>
-      <c r="R11" t="n">
+      <c r="S11" t="n">
         <v>2573</v>
       </c>
-      <c r="S11" t="n">
+      <c r="T11" t="n">
         <v>2533</v>
       </c>
-      <c r="T11" t="n">
+      <c r="U11" t="n">
         <v>2573</v>
       </c>
     </row>
@@ -1142,60 +1175,63 @@
         </is>
       </c>
       <c r="B12" t="n">
+        <v>142</v>
+      </c>
+      <c r="C12" t="n">
         <v>153</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>139</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>133</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
         <v>140</v>
       </c>
-      <c r="F12" t="n">
+      <c r="G12" t="n">
         <v>172</v>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>201</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>179</v>
       </c>
-      <c r="I12" t="n">
+      <c r="J12" t="n">
         <v>206</v>
       </c>
-      <c r="J12" t="n">
+      <c r="K12" t="n">
         <v>221</v>
       </c>
-      <c r="K12" t="n">
+      <c r="L12" t="n">
         <v>247</v>
       </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
         <v>236</v>
       </c>
-      <c r="M12" t="n">
+      <c r="N12" t="n">
         <v>237</v>
       </c>
-      <c r="N12" t="n">
+      <c r="O12" t="n">
         <v>256</v>
       </c>
-      <c r="O12" t="n">
+      <c r="P12" t="n">
         <v>293</v>
       </c>
-      <c r="P12" t="n">
+      <c r="Q12" t="n">
         <v>307</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="R12" t="n">
         <v>312</v>
       </c>
-      <c r="R12" t="n">
+      <c r="S12" t="n">
         <v>345</v>
       </c>
-      <c r="S12" t="n">
+      <c r="T12" t="n">
         <v>429</v>
       </c>
-      <c r="T12" t="n">
+      <c r="U12" t="n">
         <v>446</v>
       </c>
     </row>
@@ -1206,55 +1242,55 @@
         </is>
       </c>
       <c r="B13" t="n">
+        <v>8815</v>
+      </c>
+      <c r="C13" t="n">
         <v>8881</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>5015</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>5017</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
         <v>5012</v>
       </c>
-      <c r="F13" t="n">
+      <c r="G13" t="n">
         <v>5018</v>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>5060</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>5076</v>
-      </c>
-      <c r="I13" t="n">
-        <v>5143</v>
       </c>
       <c r="J13" t="n">
         <v>5143</v>
       </c>
       <c r="K13" t="n">
+        <v>5143</v>
+      </c>
+      <c r="L13" t="n">
         <v>5343</v>
       </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
         <v>1650</v>
       </c>
-      <c r="M13" t="n">
+      <c r="N13" t="n">
         <v>1657</v>
       </c>
-      <c r="N13" t="n">
+      <c r="O13" t="n">
         <v>1796</v>
       </c>
-      <c r="O13" t="n">
+      <c r="P13" t="n">
         <v>1801</v>
       </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
         <v>1793</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="R13" t="n">
         <v>1572</v>
-      </c>
-      <c r="R13" t="n">
-        <v>579</v>
       </c>
       <c r="S13" t="n">
         <v>579</v>
@@ -1262,6 +1298,9 @@
       <c r="T13" t="n">
         <v>579</v>
       </c>
+      <c r="U13" t="n">
+        <v>579</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1270,60 +1309,63 @@
         </is>
       </c>
       <c r="B14" t="n">
+        <v>1617</v>
+      </c>
+      <c r="C14" t="n">
         <v>1704</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>1486</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>1745</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
         <v>1735</v>
       </c>
-      <c r="F14" t="n">
+      <c r="G14" t="n">
         <v>1747</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>2625</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>2399</v>
       </c>
-      <c r="I14" t="n">
+      <c r="J14" t="n">
         <v>2530</v>
       </c>
-      <c r="J14" t="n">
+      <c r="K14" t="n">
         <v>2910</v>
       </c>
-      <c r="K14" t="n">
+      <c r="L14" t="n">
         <v>3350</v>
       </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
         <v>4914</v>
       </c>
-      <c r="M14" t="n">
+      <c r="N14" t="n">
         <v>4548</v>
       </c>
-      <c r="N14" t="n">
+      <c r="O14" t="n">
         <v>3561</v>
       </c>
-      <c r="O14" t="n">
+      <c r="P14" t="n">
         <v>2671</v>
       </c>
-      <c r="P14" t="n">
+      <c r="Q14" t="n">
         <v>1724</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="R14" t="n">
         <v>1008</v>
       </c>
-      <c r="R14" t="n">
+      <c r="S14" t="n">
         <v>315</v>
       </c>
-      <c r="S14" t="n">
+      <c r="T14" t="n">
         <v>439</v>
       </c>
-      <c r="T14" t="n">
+      <c r="U14" t="n">
         <v>434</v>
       </c>
     </row>
@@ -1334,60 +1376,63 @@
         </is>
       </c>
       <c r="B15" t="n">
+        <v>1725</v>
+      </c>
+      <c r="C15" t="n">
         <v>1796</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>1855</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>1935</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
         <v>1923</v>
       </c>
-      <c r="F15" t="n">
+      <c r="G15" t="n">
         <v>2098</v>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>1841</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>2100</v>
       </c>
-      <c r="I15" t="n">
+      <c r="J15" t="n">
         <v>2540</v>
       </c>
-      <c r="J15" t="n">
+      <c r="K15" t="n">
         <v>2711</v>
       </c>
-      <c r="K15" t="n">
+      <c r="L15" t="n">
         <v>2925</v>
       </c>
-      <c r="L15" t="n">
+      <c r="M15" t="n">
         <v>1516</v>
       </c>
-      <c r="M15" t="n">
+      <c r="N15" t="n">
         <v>1501</v>
       </c>
-      <c r="N15" t="n">
+      <c r="O15" t="n">
         <v>1638</v>
       </c>
-      <c r="O15" t="n">
+      <c r="P15" t="n">
         <v>1994</v>
       </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
         <v>2499</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="R15" t="n">
         <v>2719</v>
       </c>
-      <c r="R15" t="n">
+      <c r="S15" t="n">
         <v>3087</v>
       </c>
-      <c r="S15" t="n">
+      <c r="T15" t="n">
         <v>3170</v>
       </c>
-      <c r="T15" t="n">
+      <c r="U15" t="n">
         <v>3265</v>
       </c>
     </row>
@@ -1398,60 +1443,63 @@
         </is>
       </c>
       <c r="B16" t="n">
+        <v>1772</v>
+      </c>
+      <c r="C16" t="n">
         <v>1602</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>1477</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>1315</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
         <v>1186</v>
       </c>
-      <c r="F16" t="n">
+      <c r="G16" t="n">
         <v>1124</v>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>981</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>842</v>
       </c>
-      <c r="I16" t="n">
+      <c r="J16" t="n">
         <v>739</v>
       </c>
-      <c r="J16" t="n">
+      <c r="K16" t="n">
         <v>536</v>
       </c>
-      <c r="K16" t="n">
+      <c r="L16" t="n">
         <v>354</v>
       </c>
-      <c r="L16" t="n">
+      <c r="M16" t="n">
         <v>224</v>
       </c>
-      <c r="M16" t="n">
+      <c r="N16" t="n">
         <v>233</v>
       </c>
-      <c r="N16" t="n">
+      <c r="O16" t="n">
         <v>255</v>
       </c>
-      <c r="O16" t="n">
+      <c r="P16" t="n">
         <v>619</v>
       </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
         <v>614</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="R16" t="n">
         <v>625</v>
       </c>
-      <c r="R16" t="n">
+      <c r="S16" t="n">
         <v>314</v>
       </c>
-      <c r="S16" t="n">
+      <c r="T16" t="n">
         <v>212</v>
       </c>
-      <c r="T16" t="n">
+      <c r="U16" t="n">
         <v>225</v>
       </c>
     </row>
@@ -1462,60 +1510,63 @@
         </is>
       </c>
       <c r="B17" t="n">
+        <v>16211</v>
+      </c>
+      <c r="C17" t="n">
         <v>16598</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>12451</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>12701</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
         <v>12893</v>
       </c>
-      <c r="F17" t="n">
+      <c r="G17" t="n">
         <v>13295</v>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>14166</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>14365</v>
       </c>
-      <c r="I17" t="n">
+      <c r="J17" t="n">
         <v>16663</v>
       </c>
-      <c r="J17" t="n">
+      <c r="K17" t="n">
         <v>17164</v>
       </c>
-      <c r="K17" t="n">
+      <c r="L17" t="n">
         <v>17653</v>
       </c>
-      <c r="L17" t="n">
+      <c r="M17" t="n">
         <v>11682</v>
       </c>
-      <c r="M17" t="n">
+      <c r="N17" t="n">
         <v>11589</v>
       </c>
-      <c r="N17" t="n">
+      <c r="O17" t="n">
         <v>10997</v>
       </c>
-      <c r="O17" t="n">
+      <c r="P17" t="n">
         <v>11417</v>
       </c>
-      <c r="P17" t="n">
+      <c r="Q17" t="n">
         <v>10979</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="R17" t="n">
         <v>10361</v>
       </c>
-      <c r="R17" t="n">
+      <c r="S17" t="n">
         <v>6565</v>
       </c>
-      <c r="S17" t="n">
+      <c r="T17" t="n">
         <v>6728</v>
       </c>
-      <c r="T17" t="n">
+      <c r="U17" t="n">
         <v>6770</v>
       </c>
     </row>
@@ -1526,60 +1577,63 @@
         </is>
       </c>
       <c r="B18" t="n">
+        <v>39940</v>
+      </c>
+      <c r="C18" t="n">
         <v>40053</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>23971</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>24088</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
         <v>24991</v>
       </c>
-      <c r="F18" t="n">
+      <c r="G18" t="n">
         <v>23724</v>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>25762</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>25401</v>
       </c>
-      <c r="I18" t="n">
+      <c r="J18" t="n">
         <v>27910</v>
       </c>
-      <c r="J18" t="n">
+      <c r="K18" t="n">
         <v>28991</v>
       </c>
-      <c r="K18" t="n">
+      <c r="L18" t="n">
         <v>29696</v>
       </c>
-      <c r="L18" t="n">
+      <c r="M18" t="n">
         <v>32243</v>
       </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
         <v>34335</v>
       </c>
-      <c r="N18" t="n">
+      <c r="O18" t="n">
         <v>29477</v>
       </c>
-      <c r="O18" t="n">
+      <c r="P18" t="n">
         <v>27965</v>
       </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
         <v>21619</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="R18" t="n">
         <v>19241</v>
       </c>
-      <c r="R18" t="n">
+      <c r="S18" t="n">
         <v>12225</v>
       </c>
-      <c r="S18" t="n">
+      <c r="T18" t="n">
         <v>12337</v>
       </c>
-      <c r="T18" t="n">
+      <c r="U18" t="n">
         <v>12822</v>
       </c>
     </row>
@@ -1590,60 +1644,63 @@
         </is>
       </c>
       <c r="B19" t="n">
+        <v>1512</v>
+      </c>
+      <c r="C19" t="n">
         <v>3375</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>777</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>1132</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
         <v>997</v>
       </c>
-      <c r="F19" t="n">
+      <c r="G19" t="n">
         <v>258</v>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>262</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>1101</v>
       </c>
-      <c r="I19" t="n">
+      <c r="J19" t="n">
         <v>920</v>
       </c>
-      <c r="J19" t="n">
+      <c r="K19" t="n">
         <v>1319</v>
       </c>
-      <c r="K19" t="n">
+      <c r="L19" t="n">
         <v>971</v>
-      </c>
-      <c r="L19" t="n">
-        <v>62</v>
       </c>
       <c r="M19" t="n">
         <v>62</v>
       </c>
       <c r="N19" t="n">
+        <v>62</v>
+      </c>
+      <c r="O19" t="n">
         <v>4</v>
       </c>
-      <c r="O19" t="n">
+      <c r="P19" t="n">
         <v>504</v>
       </c>
-      <c r="P19" t="n">
+      <c r="Q19" t="n">
         <v>79</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
         <v>831</v>
       </c>
-      <c r="R19" t="n">
+      <c r="S19" t="n">
         <v>3</v>
       </c>
-      <c r="S19" t="n">
+      <c r="T19" t="n">
         <v>7</v>
       </c>
-      <c r="T19" t="n">
+      <c r="U19" t="n">
         <v>640</v>
       </c>
     </row>
@@ -1654,37 +1711,37 @@
         </is>
       </c>
       <c r="B20" t="n">
+        <v>41</v>
+      </c>
+      <c r="C20" t="n">
         <v>38</v>
       </c>
-      <c r="C20" t="n">
+      <c r="D20" t="n">
         <v>36</v>
       </c>
-      <c r="D20" t="n">
+      <c r="E20" t="n">
         <v>38</v>
       </c>
-      <c r="E20" t="n">
+      <c r="F20" t="n">
         <v>52</v>
       </c>
-      <c r="F20" t="n">
+      <c r="G20" t="n">
         <v>77</v>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>91</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>94</v>
-      </c>
-      <c r="I20" t="n">
-        <v>91</v>
       </c>
       <c r="J20" t="n">
         <v>91</v>
       </c>
       <c r="K20" t="n">
+        <v>91</v>
+      </c>
+      <c r="L20" t="n">
         <v>94</v>
-      </c>
-      <c r="L20" t="n">
-        <v>82</v>
       </c>
       <c r="M20" t="n">
         <v>82</v>
@@ -1693,7 +1750,7 @@
         <v>82</v>
       </c>
       <c r="O20" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="P20" t="n">
         <v>79</v>
@@ -1702,12 +1759,15 @@
         <v>79</v>
       </c>
       <c r="R20" t="n">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="S20" t="n">
         <v>69</v>
       </c>
       <c r="T20" t="n">
+        <v>69</v>
+      </c>
+      <c r="U20" t="n">
         <v>71</v>
       </c>
     </row>
@@ -1718,60 +1778,63 @@
         </is>
       </c>
       <c r="B21" t="n">
+        <v>2579</v>
+      </c>
+      <c r="C21" t="n">
         <v>2485</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>2319</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>2544</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
         <v>2356</v>
       </c>
-      <c r="F21" t="n">
+      <c r="G21" t="n">
         <v>1994</v>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>2109</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>2027</v>
       </c>
-      <c r="I21" t="n">
+      <c r="J21" t="n">
         <v>2200</v>
       </c>
-      <c r="J21" t="n">
+      <c r="K21" t="n">
         <v>2107</v>
       </c>
-      <c r="K21" t="n">
+      <c r="L21" t="n">
         <v>2330</v>
       </c>
-      <c r="L21" t="n">
+      <c r="M21" t="n">
         <v>2871</v>
       </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
         <v>2933</v>
       </c>
-      <c r="N21" t="n">
+      <c r="O21" t="n">
         <v>2216</v>
       </c>
-      <c r="O21" t="n">
+      <c r="P21" t="n">
         <v>1967</v>
       </c>
-      <c r="P21" t="n">
+      <c r="Q21" t="n">
         <v>2166</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
         <v>2216</v>
       </c>
-      <c r="R21" t="n">
+      <c r="S21" t="n">
         <v>753</v>
       </c>
-      <c r="S21" t="n">
+      <c r="T21" t="n">
         <v>736</v>
       </c>
-      <c r="T21" t="n">
+      <c r="U21" t="n">
         <v>708</v>
       </c>
     </row>
@@ -1782,60 +1845,63 @@
         </is>
       </c>
       <c r="B22" t="n">
+        <v>3120</v>
+      </c>
+      <c r="C22" t="n">
         <v>3230</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>1880</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>1954</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
         <v>2595</v>
       </c>
-      <c r="F22" t="n">
+      <c r="G22" t="n">
         <v>2351</v>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>2664</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>3591</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>3128</v>
       </c>
-      <c r="J22" t="n">
+      <c r="K22" t="n">
         <v>3832</v>
       </c>
-      <c r="K22" t="n">
+      <c r="L22" t="n">
         <v>4350</v>
       </c>
-      <c r="L22" t="n">
+      <c r="M22" t="n">
         <v>6841</v>
       </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
         <v>8000</v>
       </c>
-      <c r="N22" t="n">
+      <c r="O22" t="n">
         <v>6076</v>
       </c>
-      <c r="O22" t="n">
+      <c r="P22" t="n">
         <v>6032</v>
       </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
         <v>2849</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="R22" t="n">
         <v>1606</v>
       </c>
-      <c r="R22" t="n">
+      <c r="S22" t="n">
         <v>495</v>
       </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
         <v>728</v>
       </c>
-      <c r="T22" t="n">
+      <c r="U22" t="n">
         <v>832</v>
       </c>
     </row>
@@ -1846,38 +1912,38 @@
         </is>
       </c>
       <c r="B23" t="n">
+        <v>837</v>
+      </c>
+      <c r="C23" t="n">
         <v>727</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>710</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>715</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
         <v>690</v>
       </c>
-      <c r="F23" t="n">
+      <c r="G23" t="n">
         <v>761</v>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>779</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>710</v>
-      </c>
-      <c r="I23" t="n">
-        <v>731</v>
       </c>
       <c r="J23" t="n">
         <v>731</v>
       </c>
       <c r="K23" t="n">
+        <v>731</v>
+      </c>
+      <c r="L23" t="n">
         <v>688</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
       <c r="M23" t="n">
         <v>0</v>
       </c>
@@ -1900,6 +1966,9 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1910,60 +1979,63 @@
         </is>
       </c>
       <c r="B24" t="n">
+        <v>1719</v>
+      </c>
+      <c r="C24" t="n">
         <v>1816</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>1668</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>1952</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
         <v>1880</v>
       </c>
-      <c r="F24" t="n">
+      <c r="G24" t="n">
         <v>1895</v>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>1709</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>1412</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
         <v>1553</v>
       </c>
-      <c r="J24" t="n">
+      <c r="K24" t="n">
         <v>1395</v>
       </c>
-      <c r="K24" t="n">
+      <c r="L24" t="n">
         <v>1563</v>
       </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
         <v>1376</v>
       </c>
-      <c r="M24" t="n">
+      <c r="N24" t="n">
         <v>1390</v>
       </c>
-      <c r="N24" t="n">
+      <c r="O24" t="n">
         <v>1285</v>
       </c>
-      <c r="O24" t="n">
+      <c r="P24" t="n">
         <v>1679</v>
       </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
         <v>1225</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="R24" t="n">
         <v>1008</v>
       </c>
-      <c r="R24" t="n">
+      <c r="S24" t="n">
         <v>651</v>
       </c>
-      <c r="S24" t="n">
+      <c r="T24" t="n">
         <v>581</v>
       </c>
-      <c r="T24" t="n">
+      <c r="U24" t="n">
         <v>550</v>
       </c>
     </row>
@@ -1974,60 +2046,63 @@
         </is>
       </c>
       <c r="B25" t="n">
+        <v>9975</v>
+      </c>
+      <c r="C25" t="n">
         <v>11847</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>7713</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>8781</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
         <v>9300</v>
       </c>
-      <c r="F25" t="n">
+      <c r="G25" t="n">
         <v>7348</v>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>8302</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>9176</v>
       </c>
-      <c r="I25" t="n">
+      <c r="J25" t="n">
         <v>8930</v>
       </c>
-      <c r="J25" t="n">
+      <c r="K25" t="n">
         <v>9876</v>
       </c>
-      <c r="K25" t="n">
+      <c r="L25" t="n">
         <v>10326</v>
       </c>
-      <c r="L25" t="n">
+      <c r="M25" t="n">
         <v>14366</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>16437</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>12233</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>12009</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>6931</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>5795</v>
       </c>
-      <c r="R25" t="n">
+      <c r="S25" t="n">
         <v>1986</v>
       </c>
-      <c r="S25" t="n">
+      <c r="T25" t="n">
         <v>2157</v>
       </c>
-      <c r="T25" t="n">
+      <c r="U25" t="n">
         <v>2852</v>
       </c>
     </row>
@@ -2038,60 +2113,63 @@
         </is>
       </c>
       <c r="B26" t="n">
+        <v>21744</v>
+      </c>
+      <c r="C26" t="n">
         <v>19779</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>11155</v>
-      </c>
-      <c r="D26" t="n">
-        <v>9812</v>
       </c>
       <c r="E26" t="n">
         <v>9812</v>
       </c>
       <c r="F26" t="n">
+        <v>9812</v>
+      </c>
+      <c r="G26" t="n">
         <v>10422</v>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>10425</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>9559</v>
       </c>
-      <c r="I26" t="n">
+      <c r="J26" t="n">
         <v>10741</v>
       </c>
-      <c r="J26" t="n">
+      <c r="K26" t="n">
         <v>10737</v>
       </c>
-      <c r="K26" t="n">
+      <c r="L26" t="n">
         <v>11332</v>
       </c>
-      <c r="L26" t="n">
+      <c r="M26" t="n">
         <v>7974</v>
       </c>
-      <c r="M26" t="n">
+      <c r="N26" t="n">
         <v>7970</v>
       </c>
-      <c r="N26" t="n">
+      <c r="O26" t="n">
         <v>8026</v>
       </c>
-      <c r="O26" t="n">
+      <c r="P26" t="n">
         <v>7957</v>
       </c>
-      <c r="P26" t="n">
+      <c r="Q26" t="n">
         <v>8712</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="R26" t="n">
         <v>8705</v>
       </c>
-      <c r="R26" t="n">
+      <c r="S26" t="n">
         <v>5792</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>5810</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>5807</v>
       </c>
     </row>
@@ -2102,60 +2180,63 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>170</v>
+      </c>
+      <c r="C27" t="n">
         <v>165</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>143</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>134</v>
-      </c>
-      <c r="E27" t="n">
-        <v>125</v>
       </c>
       <c r="F27" t="n">
         <v>125</v>
       </c>
       <c r="G27" t="n">
+        <v>125</v>
+      </c>
+      <c r="H27" t="n">
         <v>144</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>124</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>148</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>165</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>196</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>197</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>201</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>220</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>257</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>272</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>280</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>297</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>458</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>473</v>
       </c>
     </row>
@@ -2166,60 +2247,63 @@
         </is>
       </c>
       <c r="B28" t="n">
+        <v>1327</v>
+      </c>
+      <c r="C28" t="n">
         <v>1461</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>1125</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>1273</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
         <v>1288</v>
       </c>
-      <c r="F28" t="n">
+      <c r="G28" t="n">
         <v>1469</v>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>1435</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>1439</v>
       </c>
-      <c r="I28" t="n">
+      <c r="J28" t="n">
         <v>1552</v>
       </c>
-      <c r="J28" t="n">
+      <c r="K28" t="n">
         <v>1889</v>
       </c>
-      <c r="K28" t="n">
+      <c r="L28" t="n">
         <v>1893</v>
       </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
         <v>2802</v>
       </c>
-      <c r="M28" t="n">
+      <c r="N28" t="n">
         <v>2565</v>
       </c>
-      <c r="N28" t="n">
+      <c r="O28" t="n">
         <v>1977</v>
       </c>
-      <c r="O28" t="n">
+      <c r="P28" t="n">
         <v>1489</v>
       </c>
-      <c r="P28" t="n">
+      <c r="Q28" t="n">
         <v>945</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="R28" t="n">
         <v>834</v>
       </c>
-      <c r="R28" t="n">
+      <c r="S28" t="n">
         <v>318</v>
       </c>
-      <c r="S28" t="n">
+      <c r="T28" t="n">
         <v>299</v>
       </c>
-      <c r="T28" t="n">
+      <c r="U28" t="n">
         <v>370</v>
       </c>
     </row>
@@ -2230,10 +2314,10 @@
         </is>
       </c>
       <c r="B29" t="n">
+        <v>15</v>
+      </c>
+      <c r="C29" t="n">
         <v>139</v>
-      </c>
-      <c r="C29" t="n">
-        <v>12</v>
       </c>
       <c r="D29" t="n">
         <v>12</v>
@@ -2242,7 +2326,7 @@
         <v>12</v>
       </c>
       <c r="F29" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="G29" t="n">
         <v>8</v>
@@ -2251,39 +2335,42 @@
         <v>8</v>
       </c>
       <c r="I29" t="n">
+        <v>8</v>
+      </c>
+      <c r="J29" t="n">
         <v>129</v>
       </c>
-      <c r="J29" t="n">
+      <c r="K29" t="n">
         <v>130</v>
       </c>
-      <c r="K29" t="n">
+      <c r="L29" t="n">
         <v>133</v>
       </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
         <v>84</v>
       </c>
-      <c r="M29" t="n">
+      <c r="N29" t="n">
         <v>71</v>
       </c>
-      <c r="N29" t="n">
+      <c r="O29" t="n">
         <v>68</v>
       </c>
-      <c r="O29" t="n">
+      <c r="P29" t="n">
         <v>74</v>
       </c>
-      <c r="P29" t="n">
+      <c r="Q29" t="n">
         <v>64</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="R29" t="n">
         <v>30</v>
-      </c>
-      <c r="R29" t="n">
-        <v>17</v>
       </c>
       <c r="S29" t="n">
         <v>17</v>
       </c>
       <c r="T29" t="n">
+        <v>17</v>
+      </c>
+      <c r="U29" t="n">
         <v>15</v>
       </c>
     </row>
@@ -2294,38 +2381,38 @@
         </is>
       </c>
       <c r="B30" t="n">
+        <v>984</v>
+      </c>
+      <c r="C30" t="n">
         <v>868</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>942</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>905</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
         <v>830</v>
       </c>
-      <c r="F30" t="n">
+      <c r="G30" t="n">
         <v>919</v>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>906</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>859</v>
       </c>
-      <c r="I30" t="n">
+      <c r="J30" t="n">
         <v>989</v>
       </c>
-      <c r="J30" t="n">
+      <c r="K30" t="n">
         <v>927</v>
       </c>
-      <c r="K30" t="n">
+      <c r="L30" t="n">
         <v>848</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
@@ -2348,6 +2435,9 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2358,60 +2448,63 @@
         </is>
       </c>
       <c r="B31" t="n">
+        <v>870</v>
+      </c>
+      <c r="C31" t="n">
         <v>920</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>911</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>883</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
         <v>847</v>
       </c>
-      <c r="F31" t="n">
+      <c r="G31" t="n">
         <v>913</v>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>919</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>939</v>
       </c>
-      <c r="I31" t="n">
+      <c r="J31" t="n">
         <v>977</v>
       </c>
-      <c r="J31" t="n">
+      <c r="K31" t="n">
         <v>988</v>
       </c>
-      <c r="K31" t="n">
+      <c r="L31" t="n">
         <v>1030</v>
       </c>
-      <c r="L31" t="n">
+      <c r="M31" t="n">
         <v>922</v>
       </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
         <v>976</v>
       </c>
-      <c r="N31" t="n">
+      <c r="O31" t="n">
         <v>996</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>1166</v>
       </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
         <v>1215</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="R31" t="n">
         <v>1192</v>
       </c>
-      <c r="R31" t="n">
+      <c r="S31" t="n">
         <v>1062</v>
       </c>
-      <c r="S31" t="n">
+      <c r="T31" t="n">
         <v>1061</v>
       </c>
-      <c r="T31" t="n">
+      <c r="U31" t="n">
         <v>1076</v>
       </c>
     </row>
@@ -2422,60 +2515,63 @@
         </is>
       </c>
       <c r="B32" t="n">
+        <v>25110</v>
+      </c>
+      <c r="C32" t="n">
         <v>23332</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>14288</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>13019</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
         <v>12914</v>
       </c>
-      <c r="F32" t="n">
+      <c r="G32" t="n">
         <v>13856</v>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>13837</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>12928</v>
       </c>
-      <c r="I32" t="n">
+      <c r="J32" t="n">
         <v>15462</v>
       </c>
-      <c r="J32" t="n">
+      <c r="K32" t="n">
         <v>15783</v>
       </c>
-      <c r="K32" t="n">
+      <c r="L32" t="n">
         <v>16290</v>
       </c>
-      <c r="L32" t="n">
+      <c r="M32" t="n">
         <v>12747</v>
       </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
         <v>12598</v>
       </c>
-      <c r="N32" t="n">
+      <c r="O32" t="n">
         <v>12214</v>
       </c>
-      <c r="O32" t="n">
+      <c r="P32" t="n">
         <v>11878</v>
       </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
         <v>12144</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="R32" t="n">
         <v>11929</v>
       </c>
-      <c r="R32" t="n">
+      <c r="S32" t="n">
         <v>8305</v>
       </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
         <v>8430</v>
       </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
         <v>8434</v>
       </c>
     </row>
@@ -2486,60 +2582,63 @@
         </is>
       </c>
       <c r="B33" t="n">
+        <v>35085</v>
+      </c>
+      <c r="C33" t="n">
         <v>35179</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>22001</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>21800</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
         <v>22214</v>
       </c>
-      <c r="F33" t="n">
+      <c r="G33" t="n">
         <v>21204</v>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>22139</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>22104</v>
       </c>
-      <c r="I33" t="n">
+      <c r="J33" t="n">
         <v>24392</v>
       </c>
-      <c r="J33" t="n">
+      <c r="K33" t="n">
         <v>25659</v>
       </c>
-      <c r="K33" t="n">
+      <c r="L33" t="n">
         <v>26616</v>
       </c>
-      <c r="L33" t="n">
+      <c r="M33" t="n">
         <v>27113</v>
       </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
         <v>29035</v>
       </c>
-      <c r="N33" t="n">
+      <c r="O33" t="n">
         <v>24447</v>
       </c>
-      <c r="O33" t="n">
+      <c r="P33" t="n">
         <v>23887</v>
       </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
         <v>19075</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="R33" t="n">
         <v>17724</v>
       </c>
-      <c r="R33" t="n">
+      <c r="S33" t="n">
         <v>10291</v>
       </c>
-      <c r="S33" t="n">
+      <c r="T33" t="n">
         <v>10587</v>
       </c>
-      <c r="T33" t="n">
+      <c r="U33" t="n">
         <v>11286</v>
       </c>
     </row>
@@ -2580,7 +2679,7 @@
         <v>650</v>
       </c>
       <c r="L34" t="n">
-        <v>0</v>
+        <v>650</v>
       </c>
       <c r="M34" t="n">
         <v>0</v>
@@ -2604,6 +2703,9 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2626,7 +2728,7 @@
         <v>2</v>
       </c>
       <c r="F35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G35" t="n">
         <v>3</v>
@@ -2635,7 +2737,7 @@
         <v>3</v>
       </c>
       <c r="I35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J35" t="n">
         <v>4</v>
@@ -2650,10 +2752,10 @@
         <v>4</v>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O35" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>4</v>
@@ -2670,6 +2772,9 @@
       <c r="T35" t="n">
         <v>4</v>
       </c>
+      <c r="U35" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -2678,60 +2783,63 @@
         </is>
       </c>
       <c r="B36" t="n">
+        <v>3880</v>
+      </c>
+      <c r="C36" t="n">
         <v>3868</v>
       </c>
-      <c r="C36" t="n">
+      <c r="D36" t="n">
         <v>166</v>
       </c>
-      <c r="D36" t="n">
+      <c r="E36" t="n">
         <v>305</v>
       </c>
-      <c r="E36" t="n">
+      <c r="F36" t="n">
         <v>518</v>
       </c>
-      <c r="F36" t="n">
+      <c r="G36" t="n">
         <v>3145</v>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>3229</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>3503</v>
       </c>
-      <c r="I36" t="n">
+      <c r="J36" t="n">
         <v>8527</v>
       </c>
-      <c r="J36" t="n">
+      <c r="K36" t="n">
         <v>8504</v>
       </c>
-      <c r="K36" t="n">
+      <c r="L36" t="n">
         <v>8481</v>
       </c>
-      <c r="L36" t="n">
+      <c r="M36" t="n">
         <v>8450</v>
       </c>
-      <c r="M36" t="n">
+      <c r="N36" t="n">
         <v>8442</v>
       </c>
-      <c r="N36" t="n">
+      <c r="O36" t="n">
         <v>8433</v>
       </c>
-      <c r="O36" t="n">
+      <c r="P36" t="n">
         <v>8525</v>
       </c>
-      <c r="P36" t="n">
+      <c r="Q36" t="n">
         <v>8519</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="R36" t="n">
         <v>8513</v>
       </c>
-      <c r="R36" t="n">
+      <c r="S36" t="n">
         <v>8511</v>
       </c>
-      <c r="S36" t="n">
+      <c r="T36" t="n">
         <v>8505</v>
       </c>
-      <c r="T36" t="n">
+      <c r="U36" t="n">
         <v>8498</v>
       </c>
     </row>
@@ -2742,60 +2850,63 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>2374</v>
+      </c>
+      <c r="C37" t="n">
         <v>1969</v>
       </c>
-      <c r="C37" t="n">
+      <c r="D37" t="n">
         <v>2002</v>
       </c>
-      <c r="D37" t="n">
+      <c r="E37" t="n">
         <v>1970</v>
       </c>
-      <c r="E37" t="n">
+      <c r="F37" t="n">
         <v>2162</v>
       </c>
-      <c r="F37" t="n">
+      <c r="G37" t="n">
         <v>977</v>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>1863</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>1212</v>
       </c>
-      <c r="I37" t="n">
+      <c r="J37" t="n">
         <v>425</v>
       </c>
-      <c r="J37" t="n">
+      <c r="K37" t="n">
         <v>205</v>
       </c>
-      <c r="K37" t="n">
+      <c r="L37" t="n">
         <v>-15</v>
       </c>
-      <c r="L37" t="n">
+      <c r="M37" t="n">
         <v>2584</v>
       </c>
-      <c r="M37" t="n">
+      <c r="N37" t="n">
         <v>2600</v>
       </c>
-      <c r="N37" t="n">
+      <c r="O37" t="n">
         <v>2171</v>
       </c>
-      <c r="O37" t="n">
+      <c r="P37" t="n">
         <v>971</v>
       </c>
-      <c r="P37" t="n">
+      <c r="Q37" t="n">
         <v>-567</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="R37" t="n">
         <v>-1565</v>
       </c>
-      <c r="R37" t="n">
+      <c r="S37" t="n">
         <v>-1157</v>
       </c>
-      <c r="S37" t="n">
+      <c r="T37" t="n">
         <v>-1331</v>
       </c>
-      <c r="T37" t="n">
+      <c r="U37" t="n">
         <v>-1570</v>
       </c>
     </row>
@@ -2806,60 +2917,63 @@
         </is>
       </c>
       <c r="B38" t="n">
+        <v>-1964</v>
+      </c>
+      <c r="C38" t="n">
         <v>-1531</v>
       </c>
-      <c r="C38" t="n">
+      <c r="D38" t="n">
         <v>-745</v>
       </c>
-      <c r="D38" t="n">
+      <c r="E38" t="n">
         <v>-538</v>
       </c>
-      <c r="E38" t="n">
+      <c r="F38" t="n">
         <v>-440</v>
       </c>
-      <c r="F38" t="n">
+      <c r="G38" t="n">
         <v>-2150</v>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>-2019</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>-1971</v>
       </c>
-      <c r="I38" t="n">
+      <c r="J38" t="n">
         <v>-5911</v>
       </c>
-      <c r="J38" t="n">
+      <c r="K38" t="n">
         <v>-5861</v>
       </c>
-      <c r="K38" t="n">
+      <c r="L38" t="n">
         <v>-5864</v>
       </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
         <v>-5754</v>
       </c>
-      <c r="M38" t="n">
+      <c r="N38" t="n">
         <v>-5626</v>
       </c>
-      <c r="N38" t="n">
+      <c r="O38" t="n">
         <v>-5460</v>
-      </c>
-      <c r="O38" t="n">
-        <v>-5230</v>
       </c>
       <c r="P38" t="n">
         <v>-5230</v>
       </c>
       <c r="Q38" t="n">
+        <v>-5230</v>
+      </c>
+      <c r="R38" t="n">
         <v>-5232</v>
-      </c>
-      <c r="R38" t="n">
-        <v>-5234</v>
       </c>
       <c r="S38" t="n">
         <v>-5234</v>
       </c>
       <c r="T38" t="n">
+        <v>-5234</v>
+      </c>
+      <c r="U38" t="n">
         <v>-5189</v>
       </c>
     </row>
@@ -2870,60 +2984,63 @@
         </is>
       </c>
       <c r="B39" t="n">
+        <v>-87</v>
+      </c>
+      <c r="C39" t="n">
         <v>-84</v>
       </c>
-      <c r="C39" t="n">
+      <c r="D39" t="n">
         <v>-105</v>
       </c>
-      <c r="D39" t="n">
+      <c r="E39" t="n">
         <v>-101</v>
       </c>
-      <c r="E39" t="n">
+      <c r="F39" t="n">
         <v>-115</v>
       </c>
-      <c r="F39" t="n">
+      <c r="G39" t="n">
         <v>-105</v>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>-103</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>-100</v>
       </c>
-      <c r="I39" t="n">
+      <c r="J39" t="n">
         <v>-177</v>
       </c>
-      <c r="J39" t="n">
+      <c r="K39" t="n">
         <v>-170</v>
       </c>
-      <c r="K39" t="n">
+      <c r="L39" t="n">
         <v>-176</v>
       </c>
-      <c r="L39" t="n">
+      <c r="M39" t="n">
         <v>-154</v>
       </c>
-      <c r="M39" t="n">
+      <c r="N39" t="n">
         <v>-120</v>
       </c>
-      <c r="N39" t="n">
+      <c r="O39" t="n">
         <v>-118</v>
       </c>
-      <c r="O39" t="n">
+      <c r="P39" t="n">
         <v>-192</v>
       </c>
-      <c r="P39" t="n">
+      <c r="Q39" t="n">
         <v>-182</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="R39" t="n">
         <v>-203</v>
       </c>
-      <c r="R39" t="n">
+      <c r="S39" t="n">
         <v>-190</v>
       </c>
-      <c r="S39" t="n">
+      <c r="T39" t="n">
         <v>-194</v>
       </c>
-      <c r="T39" t="n">
+      <c r="U39" t="n">
         <v>-207</v>
       </c>
     </row>
@@ -2934,60 +3051,63 @@
         </is>
       </c>
       <c r="B40" t="n">
+        <v>4855</v>
+      </c>
+      <c r="C40" t="n">
         <v>4874</v>
       </c>
-      <c r="C40" t="n">
+      <c r="D40" t="n">
         <v>1970</v>
       </c>
-      <c r="D40" t="n">
+      <c r="E40" t="n">
         <v>2288</v>
       </c>
-      <c r="E40" t="n">
+      <c r="F40" t="n">
         <v>2777</v>
       </c>
-      <c r="F40" t="n">
+      <c r="G40" t="n">
         <v>2520</v>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>3623</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>3297</v>
       </c>
-      <c r="I40" t="n">
+      <c r="J40" t="n">
         <v>3518</v>
       </c>
-      <c r="J40" t="n">
+      <c r="K40" t="n">
         <v>3332</v>
       </c>
-      <c r="K40" t="n">
+      <c r="L40" t="n">
         <v>3080</v>
       </c>
-      <c r="L40" t="n">
+      <c r="M40" t="n">
         <v>5130</v>
       </c>
-      <c r="M40" t="n">
+      <c r="N40" t="n">
         <v>5300</v>
       </c>
-      <c r="N40" t="n">
+      <c r="O40" t="n">
         <v>5030</v>
       </c>
-      <c r="O40" t="n">
+      <c r="P40" t="n">
         <v>4078</v>
       </c>
-      <c r="P40" t="n">
+      <c r="Q40" t="n">
         <v>2544</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="R40" t="n">
         <v>1517</v>
       </c>
-      <c r="R40" t="n">
+      <c r="S40" t="n">
         <v>1934</v>
       </c>
-      <c r="S40" t="n">
+      <c r="T40" t="n">
         <v>1750</v>
       </c>
-      <c r="T40" t="n">
+      <c r="U40" t="n">
         <v>1536</v>
       </c>
     </row>
@@ -2998,60 +3118,63 @@
         </is>
       </c>
       <c r="B41" t="n">
+        <v>1177</v>
+      </c>
+      <c r="C41" t="n">
         <v>1255</v>
       </c>
-      <c r="C41" t="n">
+      <c r="D41" t="n">
         <v>1294</v>
       </c>
-      <c r="D41" t="n">
+      <c r="E41" t="n">
         <v>1379</v>
       </c>
-      <c r="E41" t="n">
+      <c r="F41" t="n">
         <v>1469</v>
       </c>
-      <c r="F41" t="n">
+      <c r="G41" t="n">
         <v>1648</v>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>1946</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>2064</v>
       </c>
-      <c r="I41" t="n">
+      <c r="J41" t="n">
         <v>2299</v>
       </c>
-      <c r="J41" t="n">
+      <c r="K41" t="n">
         <v>2446</v>
       </c>
-      <c r="K41" t="n">
+      <c r="L41" t="n">
         <v>4419</v>
       </c>
-      <c r="L41" t="n">
+      <c r="M41" t="n">
         <v>2227</v>
       </c>
-      <c r="M41" t="n">
+      <c r="N41" t="n">
         <v>2450</v>
       </c>
-      <c r="N41" t="n">
+      <c r="O41" t="n">
         <v>2391</v>
       </c>
-      <c r="O41" t="n">
+      <c r="P41" t="n">
         <v>2915</v>
       </c>
-      <c r="P41" t="n">
+      <c r="Q41" t="n">
         <v>2921</v>
       </c>
-      <c r="Q41" t="n">
+      <c r="R41" t="n">
         <v>3054</v>
       </c>
-      <c r="R41" t="n">
+      <c r="S41" t="n">
         <v>721</v>
       </c>
-      <c r="S41" t="n">
+      <c r="T41" t="n">
         <v>733</v>
       </c>
-      <c r="T41" t="n">
+      <c r="U41" t="n">
         <v>769</v>
       </c>
     </row>
@@ -3065,57 +3188,60 @@
         <v>0</v>
       </c>
       <c r="C42" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" t="n">
         <v>48</v>
-      </c>
-      <c r="D42" t="n">
-        <v>47</v>
       </c>
       <c r="E42" t="n">
         <v>47</v>
       </c>
       <c r="F42" t="n">
+        <v>47</v>
+      </c>
+      <c r="G42" t="n">
         <v>49</v>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>45</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>43</v>
       </c>
-      <c r="I42" t="n">
+      <c r="J42" t="n">
         <v>146</v>
       </c>
-      <c r="J42" t="n">
+      <c r="K42" t="n">
         <v>139</v>
       </c>
-      <c r="K42" t="n">
+      <c r="L42" t="n">
         <v>136</v>
       </c>
-      <c r="L42" t="n">
+      <c r="M42" t="n">
         <v>126</v>
       </c>
-      <c r="M42" t="n">
+      <c r="N42" t="n">
         <v>127</v>
       </c>
-      <c r="N42" t="n">
+      <c r="O42" t="n">
         <v>151</v>
       </c>
-      <c r="O42" t="n">
+      <c r="P42" t="n">
         <v>167</v>
       </c>
-      <c r="P42" t="n">
+      <c r="Q42" t="n">
         <v>164</v>
       </c>
-      <c r="Q42" t="n">
+      <c r="R42" t="n">
         <v>162</v>
       </c>
-      <c r="R42" t="n">
+      <c r="S42" t="n">
         <v>376</v>
       </c>
-      <c r="S42" t="n">
+      <c r="T42" t="n">
         <v>372</v>
       </c>
-      <c r="T42" t="n">
+      <c r="U42" t="n">
         <v>350</v>
       </c>
     </row>
@@ -3153,33 +3279,36 @@
         <v>0</v>
       </c>
       <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>879</v>
       </c>
-      <c r="L43" t="n">
+      <c r="M43" t="n">
         <v>789</v>
       </c>
-      <c r="M43" t="n">
+      <c r="N43" t="n">
         <v>836</v>
       </c>
-      <c r="N43" t="n">
+      <c r="O43" t="n">
         <v>949</v>
-      </c>
-      <c r="O43" t="n">
-        <v>957</v>
       </c>
       <c r="P43" t="n">
         <v>957</v>
       </c>
       <c r="Q43" t="n">
+        <v>957</v>
+      </c>
+      <c r="R43" t="n">
         <v>909</v>
       </c>
-      <c r="R43" t="n">
+      <c r="S43" t="n">
         <v>828</v>
       </c>
-      <c r="S43" t="n">
+      <c r="T43" t="n">
         <v>794</v>
       </c>
-      <c r="T43" t="n">
+      <c r="U43" t="n">
         <v>702</v>
       </c>
     </row>
@@ -3217,33 +3346,36 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" t="n">
         <v>344</v>
       </c>
-      <c r="L44" t="n">
+      <c r="M44" t="n">
         <v>335</v>
       </c>
-      <c r="M44" t="n">
+      <c r="N44" t="n">
         <v>330</v>
       </c>
-      <c r="N44" t="n">
+      <c r="O44" t="n">
         <v>325</v>
       </c>
-      <c r="O44" t="n">
+      <c r="P44" t="n">
         <v>316</v>
       </c>
-      <c r="P44" t="n">
+      <c r="Q44" t="n">
         <v>312</v>
       </c>
-      <c r="Q44" t="n">
+      <c r="R44" t="n">
         <v>308</v>
       </c>
-      <c r="R44" t="n">
+      <c r="S44" t="n">
         <v>311</v>
       </c>
-      <c r="S44" t="n">
+      <c r="T44" t="n">
         <v>307</v>
       </c>
-      <c r="T44" t="n">
+      <c r="U44" t="n">
         <v>303</v>
       </c>
     </row>
@@ -3281,33 +3413,36 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" t="n">
         <v>514</v>
       </c>
-      <c r="L45" t="n">
+      <c r="M45" t="n">
         <v>433</v>
       </c>
-      <c r="M45" t="n">
+      <c r="N45" t="n">
         <v>485</v>
       </c>
-      <c r="N45" t="n">
+      <c r="O45" t="n">
         <v>602</v>
       </c>
-      <c r="O45" t="n">
+      <c r="P45" t="n">
         <v>619</v>
       </c>
-      <c r="P45" t="n">
+      <c r="Q45" t="n">
         <v>624</v>
       </c>
-      <c r="Q45" t="n">
+      <c r="R45" t="n">
         <v>580</v>
       </c>
-      <c r="R45" t="n">
+      <c r="S45" t="n">
         <v>508</v>
       </c>
-      <c r="S45" t="n">
+      <c r="T45" t="n">
         <v>478</v>
       </c>
-      <c r="T45" t="n">
+      <c r="U45" t="n">
         <v>390</v>
       </c>
     </row>
@@ -3322,65 +3457,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T27"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -3391,60 +3529,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>7481</v>
+      </c>
+      <c r="C2" t="n">
         <v>10256</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>7635</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>6740</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>8585</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>7223</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>6659</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>7429</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>7946</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>6348</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>7722</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>8510</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>7282</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>7896</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>6609</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>5243</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>8091</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>2809</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>2238</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>2019</v>
       </c>
     </row>
@@ -3455,60 +3596,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>5470</v>
+      </c>
+      <c r="C3" t="n">
         <v>8858</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>6241</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>5629</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>6561</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>7239</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4356</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>5685</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>6421</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>4962</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>8778</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>7802</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>5887</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>4930</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>3692</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>2957</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>6864</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>2034</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>1434</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>1457</v>
       </c>
     </row>
@@ -3519,60 +3663,63 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>494</v>
+      </c>
+      <c r="C4" t="n">
         <v>432</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>360</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>344</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>326</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>352</v>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>285</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>268</v>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>308</v>
       </c>
-      <c r="J4" t="n">
+      <c r="K4" t="n">
         <v>315</v>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>190</v>
       </c>
-      <c r="L4" t="n">
+      <c r="M4" t="n">
         <v>145</v>
       </c>
-      <c r="M4" t="n">
+      <c r="N4" t="n">
         <v>157</v>
       </c>
-      <c r="N4" t="n">
+      <c r="O4" t="n">
         <v>183</v>
       </c>
-      <c r="O4" t="n">
+      <c r="P4" t="n">
         <v>199</v>
       </c>
-      <c r="P4" t="n">
+      <c r="Q4" t="n">
         <v>53</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="R4" t="n">
         <v>317</v>
       </c>
-      <c r="R4" t="n">
+      <c r="S4" t="n">
         <v>99</v>
       </c>
-      <c r="S4" t="n">
+      <c r="T4" t="n">
         <v>110</v>
       </c>
-      <c r="T4" t="n">
+      <c r="U4" t="n">
         <v>109</v>
       </c>
     </row>
@@ -3583,60 +3730,63 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>562</v>
+      </c>
+      <c r="C5" t="n">
         <v>593</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>612</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>724</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
         <v>549</v>
       </c>
-      <c r="F5" t="n">
+      <c r="G5" t="n">
         <v>645</v>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>592</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>591</v>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>638</v>
       </c>
-      <c r="J5" t="n">
+      <c r="K5" t="n">
         <v>522</v>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>426</v>
       </c>
-      <c r="L5" t="n">
+      <c r="M5" t="n">
         <v>326</v>
       </c>
-      <c r="M5" t="n">
+      <c r="N5" t="n">
         <v>325</v>
       </c>
-      <c r="N5" t="n">
+      <c r="O5" t="n">
         <v>322</v>
       </c>
-      <c r="O5" t="n">
+      <c r="P5" t="n">
         <v>318</v>
       </c>
-      <c r="P5" t="n">
+      <c r="Q5" t="n">
         <v>308</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="R5" t="n">
         <v>330</v>
       </c>
-      <c r="R5" t="n">
+      <c r="S5" t="n">
         <v>253</v>
       </c>
-      <c r="S5" t="n">
+      <c r="T5" t="n">
         <v>208</v>
       </c>
-      <c r="T5" t="n">
+      <c r="U5" t="n">
         <v>209</v>
       </c>
     </row>
@@ -3647,60 +3797,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>16</v>
+      </c>
+      <c r="C6" t="n">
         <v>45</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>8</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>43</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>8</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>7</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>6</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>9</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>18</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>22</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>71</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>8</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>10</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>8</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>17</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>22</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>42</v>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3711,60 +3864,63 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>6542</v>
+      </c>
+      <c r="C7" t="n">
         <v>9928</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>7221</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6740</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>7444</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>8243</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>5254</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>6553</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>7385</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>5821</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>9465</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>8376</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>6560</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>5468</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>4290</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>3686</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>8164</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>2416</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>1754</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>1781</v>
       </c>
     </row>
@@ -3775,7 +3931,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -3784,51 +3940,54 @@
         <v>0</v>
       </c>
       <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="n">
         <v>-7</v>
       </c>
-      <c r="F8" t="n">
+      <c r="G8" t="n">
         <v>208</v>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>-4</v>
       </c>
-      <c r="I8" t="n">
-        <v>0</v>
-      </c>
       <c r="J8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" t="n">
         <v>3</v>
       </c>
-      <c r="K8" t="n">
+      <c r="L8" t="n">
         <v>199</v>
       </c>
-      <c r="L8" t="n">
+      <c r="M8" t="n">
         <v>22</v>
       </c>
-      <c r="M8" t="n">
+      <c r="N8" t="n">
         <v>32</v>
       </c>
-      <c r="N8" t="n">
+      <c r="O8" t="n">
         <v>-3</v>
       </c>
-      <c r="O8" t="n">
-        <v>0</v>
-      </c>
       <c r="P8" t="n">
         <v>0</v>
       </c>
       <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
         <v>17</v>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
       <c r="S8" t="n">
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>6</v>
       </c>
     </row>
@@ -3839,60 +3998,63 @@
         </is>
       </c>
       <c r="B9" t="n">
+        <v>976</v>
+      </c>
+      <c r="C9" t="n">
         <v>328</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>414</v>
       </c>
-      <c r="D9" t="n">
-        <v>0</v>
-      </c>
       <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="n">
         <v>1134</v>
       </c>
-      <c r="F9" t="n">
+      <c r="G9" t="n">
         <v>-812</v>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>1410</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>872</v>
       </c>
-      <c r="I9" t="n">
+      <c r="J9" t="n">
         <v>561</v>
       </c>
-      <c r="J9" t="n">
+      <c r="K9" t="n">
         <v>530</v>
       </c>
-      <c r="K9" t="n">
+      <c r="L9" t="n">
         <v>-1544</v>
       </c>
-      <c r="L9" t="n">
+      <c r="M9" t="n">
         <v>156</v>
       </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
         <v>754</v>
       </c>
-      <c r="N9" t="n">
+      <c r="O9" t="n">
         <v>2425</v>
       </c>
-      <c r="O9" t="n">
+      <c r="P9" t="n">
         <v>2319</v>
       </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
         <v>1557</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="R9" t="n">
         <v>-56</v>
       </c>
-      <c r="R9" t="n">
+      <c r="S9" t="n">
         <v>393</v>
       </c>
-      <c r="S9" t="n">
+      <c r="T9" t="n">
         <v>484</v>
       </c>
-      <c r="T9" t="n">
+      <c r="U9" t="n">
         <v>244</v>
       </c>
     </row>
@@ -3903,485 +4065,506 @@
         </is>
       </c>
       <c r="B10" t="n">
+        <v>6</v>
+      </c>
+      <c r="C10" t="n">
         <v>40</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>10</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>4</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
         <v>12</v>
       </c>
-      <c r="F10" t="n">
+      <c r="G10" t="n">
         <v>5</v>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>3</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>30</v>
       </c>
-      <c r="I10" t="n">
+      <c r="J10" t="n">
         <v>14</v>
       </c>
-      <c r="J10" t="n">
+      <c r="K10" t="n">
         <v>13</v>
       </c>
-      <c r="K10" t="n">
+      <c r="L10" t="n">
         <v>16</v>
       </c>
-      <c r="L10" t="n">
+      <c r="M10" t="n">
         <v>21</v>
       </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
         <v>12</v>
       </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
       <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
         <v>8</v>
       </c>
-      <c r="P10" t="n">
+      <c r="Q10" t="n">
         <v>12</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
         <v>22</v>
       </c>
-      <c r="R10" t="n">
+      <c r="S10" t="n">
         <v>11</v>
       </c>
-      <c r="S10" t="n">
+      <c r="T10" t="n">
         <v>14</v>
       </c>
-      <c r="T10" t="n">
+      <c r="U10" t="n">
         <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Interest Expense</t>
+          <t>Gain (Loss) on Extinguishment of Debt</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>-285</v>
+        <v>-9</v>
       </c>
       <c r="C11" t="n">
-        <v>-187</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>-163</v>
+        <v>-10</v>
       </c>
       <c r="F11" t="n">
-        <v>-213</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>-163</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-152</v>
+        <v>-202</v>
       </c>
       <c r="I11" t="n">
-        <v>-173</v>
+        <v>-58</v>
       </c>
       <c r="J11" t="n">
-        <v>-151</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>-105</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-105</v>
+        <v>0</v>
       </c>
       <c r="N11" t="n">
-        <v>-103</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>-122</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-125</v>
+        <v>-57</v>
       </c>
       <c r="Q11" t="n">
-        <v>-127</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>-99</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-96</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>-98</v>
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Nonoperating Income (Expense)</t>
+          <t>Interest Expense</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>-245</v>
+        <v>-310</v>
       </c>
       <c r="C12" t="n">
-        <v>-176</v>
+        <v>-285</v>
       </c>
       <c r="D12" t="n">
-        <v>-153</v>
+        <v>-187</v>
       </c>
       <c r="E12" t="n">
-        <v>-149</v>
+        <v>-148</v>
       </c>
       <c r="F12" t="n">
-        <v>-202</v>
+        <v>-163</v>
       </c>
       <c r="G12" t="n">
-        <v>-358</v>
+        <v>-213</v>
       </c>
       <c r="H12" t="n">
-        <v>-177</v>
+        <v>-163</v>
       </c>
       <c r="I12" t="n">
-        <v>-153</v>
+        <v>-152</v>
       </c>
       <c r="J12" t="n">
-        <v>-133</v>
+        <v>-173</v>
       </c>
       <c r="K12" t="n">
+        <v>-151</v>
+      </c>
+      <c r="L12" t="n">
+        <v>-148</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-105</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-105</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-103</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-122</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-125</v>
+      </c>
+      <c r="R12" t="n">
         <v>-127</v>
       </c>
-      <c r="L12" t="n">
-        <v>-73</v>
-      </c>
-      <c r="M12" t="n">
-        <v>-89</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-118</v>
-      </c>
-      <c r="O12" t="n">
-        <v>-156</v>
-      </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>-99</v>
       </c>
-      <c r="Q12" t="n">
-        <v>-111</v>
-      </c>
-      <c r="R12" t="n">
-        <v>-52</v>
-      </c>
-      <c r="S12" t="n">
-        <v>-70</v>
-      </c>
       <c r="T12" t="n">
-        <v>-100</v>
+        <v>-96</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-98</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Income Before Provision for Income Taxes</t>
+          <t>Nonoperating Income (Expense)</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83</v>
+        <v>-313</v>
       </c>
       <c r="C13" t="n">
-        <v>238</v>
+        <v>-245</v>
       </c>
       <c r="D13" t="n">
+        <v>-176</v>
+      </c>
+      <c r="E13" t="n">
         <v>-153</v>
       </c>
-      <c r="E13" t="n">
-        <v>985</v>
-      </c>
       <c r="F13" t="n">
-        <v>-1014</v>
+        <v>-149</v>
       </c>
       <c r="G13" t="n">
-        <v>1052</v>
+        <v>-202</v>
       </c>
       <c r="H13" t="n">
-        <v>695</v>
+        <v>-358</v>
       </c>
       <c r="I13" t="n">
-        <v>408</v>
+        <v>-177</v>
       </c>
       <c r="J13" t="n">
-        <v>397</v>
+        <v>-153</v>
       </c>
       <c r="K13" t="n">
-        <v>-1671</v>
+        <v>-133</v>
       </c>
       <c r="L13" t="n">
-        <v>83</v>
+        <v>-127</v>
       </c>
       <c r="M13" t="n">
-        <v>665</v>
+        <v>-73</v>
       </c>
       <c r="N13" t="n">
-        <v>2307</v>
+        <v>-89</v>
       </c>
       <c r="O13" t="n">
-        <v>2163</v>
+        <v>-118</v>
       </c>
       <c r="P13" t="n">
-        <v>1458</v>
+        <v>-156</v>
       </c>
       <c r="Q13" t="n">
-        <v>-167</v>
+        <v>-99</v>
       </c>
       <c r="R13" t="n">
-        <v>341</v>
+        <v>-111</v>
       </c>
       <c r="S13" t="n">
-        <v>414</v>
+        <v>-52</v>
       </c>
       <c r="T13" t="n">
-        <v>144</v>
+        <v>-70</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-100</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Provision for Income Taxes</t>
+          <t>Income Before Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-42</v>
+        <v>663</v>
       </c>
       <c r="C14" t="n">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="D14" t="n">
-        <v>-49</v>
+        <v>238</v>
       </c>
       <c r="E14" t="n">
-        <v>235</v>
+        <v>-153</v>
       </c>
       <c r="F14" t="n">
-        <v>-247</v>
+        <v>985</v>
       </c>
       <c r="G14" t="n">
-        <v>314</v>
+        <v>-1014</v>
       </c>
       <c r="H14" t="n">
-        <v>184</v>
+        <v>1052</v>
       </c>
       <c r="I14" t="n">
-        <v>65</v>
+        <v>695</v>
       </c>
       <c r="J14" t="n">
-        <v>89</v>
+        <v>408</v>
       </c>
       <c r="K14" t="n">
-        <v>-336</v>
+        <v>397</v>
       </c>
       <c r="L14" t="n">
-        <v>16</v>
+        <v>-1671</v>
       </c>
       <c r="M14" t="n">
-        <v>152</v>
+        <v>83</v>
       </c>
       <c r="N14" t="n">
-        <v>571</v>
+        <v>665</v>
       </c>
       <c r="O14" t="n">
-        <v>545</v>
+        <v>2307</v>
       </c>
       <c r="P14" t="n">
-        <v>380</v>
+        <v>2163</v>
       </c>
       <c r="Q14" t="n">
-        <v>-85</v>
+        <v>1458</v>
       </c>
       <c r="R14" t="n">
-        <v>92</v>
+        <v>-167</v>
       </c>
       <c r="S14" t="n">
-        <v>101</v>
+        <v>341</v>
       </c>
       <c r="T14" t="n">
-        <v>23</v>
+        <v>414</v>
+      </c>
+      <c r="U14" t="n">
+        <v>144</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
+          <t>Provision for Income Taxes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>125</v>
+        <v>157</v>
       </c>
       <c r="C15" t="n">
+        <v>-42</v>
+      </c>
+      <c r="D15" t="n">
+        <v>86</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="F15" t="n">
+        <v>235</v>
+      </c>
+      <c r="G15" t="n">
+        <v>-247</v>
+      </c>
+      <c r="H15" t="n">
+        <v>314</v>
+      </c>
+      <c r="I15" t="n">
+        <v>184</v>
+      </c>
+      <c r="J15" t="n">
+        <v>65</v>
+      </c>
+      <c r="K15" t="n">
+        <v>89</v>
+      </c>
+      <c r="L15" t="n">
+        <v>-336</v>
+      </c>
+      <c r="M15" t="n">
+        <v>16</v>
+      </c>
+      <c r="N15" t="n">
         <v>152</v>
       </c>
-      <c r="D15" t="n">
-        <v>-104</v>
-      </c>
-      <c r="E15" t="n">
-        <v>750</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-767</v>
-      </c>
-      <c r="G15" t="n">
-        <v>738</v>
-      </c>
-      <c r="H15" t="n">
-        <v>511</v>
-      </c>
-      <c r="I15" t="n">
-        <v>343</v>
-      </c>
-      <c r="J15" t="n">
-        <v>308</v>
-      </c>
-      <c r="K15" t="n">
-        <v>-1335</v>
-      </c>
-      <c r="L15" t="n">
-        <v>67</v>
-      </c>
-      <c r="M15" t="n">
-        <v>513</v>
-      </c>
-      <c r="N15" t="n">
-        <v>1736</v>
-      </c>
       <c r="O15" t="n">
-        <v>1618</v>
+        <v>571</v>
       </c>
       <c r="P15" t="n">
-        <v>1078</v>
+        <v>545</v>
       </c>
       <c r="Q15" t="n">
-        <v>-82</v>
+        <v>380</v>
       </c>
       <c r="R15" t="n">
-        <v>249</v>
+        <v>-85</v>
       </c>
       <c r="S15" t="n">
-        <v>313</v>
+        <v>92</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>101</v>
+      </c>
+      <c r="U15" t="n">
+        <v>23</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Preferred Stock Dividends, Income Statement Impact</t>
+          <t>Net Income (Loss), Including Portion Attributable to Noncontrolling Interest</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>506</v>
       </c>
       <c r="C16" t="n">
-        <v>17</v>
+        <v>125</v>
       </c>
       <c r="D16" t="n">
-        <v>17</v>
+        <v>152</v>
       </c>
       <c r="E16" t="n">
-        <v>17</v>
+        <v>-104</v>
       </c>
       <c r="F16" t="n">
-        <v>17</v>
+        <v>750</v>
       </c>
       <c r="G16" t="n">
-        <v>17</v>
+        <v>-767</v>
       </c>
       <c r="H16" t="n">
-        <v>17</v>
+        <v>738</v>
       </c>
       <c r="I16" t="n">
-        <v>17</v>
+        <v>511</v>
       </c>
       <c r="J16" t="n">
-        <v>17</v>
+        <v>343</v>
       </c>
       <c r="K16" t="n">
-        <v>4</v>
+        <v>308</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1335</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>513</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>1736</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1618</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>1078</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>249</v>
       </c>
       <c r="T16" t="n">
+        <v>313</v>
+      </c>
+      <c r="U16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Net Income (Loss) Available to Common Stockholders, Basic</t>
+          <t>Preferred Stock Dividends, Income Statement Impact</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>108</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>135</v>
+        <v>17</v>
       </c>
       <c r="D17" t="n">
-        <v>-121</v>
+        <v>17</v>
       </c>
       <c r="E17" t="n">
-        <v>733</v>
+        <v>17</v>
       </c>
       <c r="F17" t="n">
-        <v>-784</v>
+        <v>17</v>
       </c>
       <c r="G17" t="n">
-        <v>721</v>
+        <v>17</v>
       </c>
       <c r="H17" t="n">
-        <v>494</v>
+        <v>17</v>
       </c>
       <c r="I17" t="n">
-        <v>326</v>
+        <v>17</v>
       </c>
       <c r="J17" t="n">
-        <v>291</v>
+        <v>17</v>
       </c>
       <c r="K17" t="n">
-        <v>-1339</v>
+        <v>17</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M17" t="n">
         <v>0</v>
@@ -4405,306 +4588,321 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Basic</t>
+          <t>Net Income (Loss) Available to Common Stockholders, Basic</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>207</v>
+        <v>489</v>
       </c>
       <c r="C18" t="n">
-        <v>193</v>
+        <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>196</v>
+        <v>135</v>
       </c>
       <c r="E18" t="n">
-        <v>198</v>
+        <v>-121</v>
       </c>
       <c r="F18" t="n">
-        <v>207</v>
+        <v>733</v>
       </c>
       <c r="G18" t="n">
-        <v>208</v>
+        <v>-784</v>
       </c>
       <c r="H18" t="n">
-        <v>209</v>
+        <v>721</v>
       </c>
       <c r="I18" t="n">
-        <v>230</v>
+        <v>494</v>
       </c>
       <c r="J18" t="n">
-        <v>231</v>
+        <v>326</v>
       </c>
       <c r="K18" t="n">
-        <v>230</v>
+        <v>291</v>
       </c>
       <c r="L18" t="n">
-        <v>235</v>
+        <v>-1339</v>
       </c>
       <c r="M18" t="n">
-        <v>237</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>244</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>245</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>248</v>
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Basic</t>
+          <t>Number of Shares - Basic</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.52</v>
+        <v>211</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7</v>
+        <v>207</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.62</v>
+        <v>193</v>
       </c>
       <c r="E19" t="n">
-        <v>3.7</v>
+        <v>196</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.79</v>
+        <v>198</v>
       </c>
       <c r="G19" t="n">
-        <v>3.47</v>
+        <v>207</v>
       </c>
       <c r="H19" t="n">
-        <v>2.36</v>
+        <v>208</v>
       </c>
       <c r="I19" t="n">
-        <v>1.42</v>
+        <v>209</v>
       </c>
       <c r="J19" t="n">
-        <v>1.26</v>
+        <v>230</v>
       </c>
       <c r="K19" t="n">
-        <v>-5.82</v>
+        <v>231</v>
       </c>
       <c r="L19" t="n">
-        <v>0.29</v>
+        <v>230</v>
       </c>
       <c r="M19" t="n">
-        <v>2.16</v>
+        <v>235</v>
       </c>
       <c r="N19" t="n">
-        <v>7.17</v>
+        <v>237</v>
       </c>
       <c r="O19" t="n">
-        <v>6.6</v>
+        <v>242</v>
       </c>
       <c r="P19" t="n">
-        <v>4.4</v>
+        <v>245</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.33</v>
+        <v>245</v>
       </c>
       <c r="R19" t="n">
-        <v>1.02</v>
+        <v>245</v>
       </c>
       <c r="S19" t="n">
-        <v>1.28</v>
+        <v>244</v>
       </c>
       <c r="T19" t="n">
-        <v>0.49</v>
+        <v>245</v>
+      </c>
+      <c r="U19" t="n">
+        <v>248</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Number of Shares - Diluted</t>
+          <t>Earnings Per Share, Basic</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>208</v>
+        <v>2.32</v>
       </c>
       <c r="C20" t="n">
-        <v>195</v>
+        <v>0.52</v>
       </c>
       <c r="D20" t="n">
-        <v>196</v>
+        <v>0.7</v>
       </c>
       <c r="E20" t="n">
-        <v>203</v>
+        <v>-0.62</v>
       </c>
       <c r="F20" t="n">
-        <v>207</v>
+        <v>3.7</v>
       </c>
       <c r="G20" t="n">
-        <v>214</v>
+        <v>-3.79</v>
       </c>
       <c r="H20" t="n">
-        <v>214</v>
+        <v>3.47</v>
       </c>
       <c r="I20" t="n">
-        <v>232</v>
+        <v>2.36</v>
       </c>
       <c r="J20" t="n">
-        <v>232</v>
+        <v>1.42</v>
       </c>
       <c r="K20" t="n">
-        <v>230</v>
+        <v>1.26</v>
       </c>
       <c r="L20" t="n">
-        <v>235</v>
+        <v>-5.82</v>
       </c>
       <c r="M20" t="n">
-        <v>237</v>
+        <v>0.29</v>
       </c>
       <c r="N20" t="n">
-        <v>242</v>
+        <v>2.16</v>
       </c>
       <c r="O20" t="n">
-        <v>245</v>
+        <v>7.17</v>
       </c>
       <c r="P20" t="n">
-        <v>245</v>
+        <v>6.6</v>
       </c>
       <c r="Q20" t="n">
-        <v>245</v>
+        <v>4.4</v>
       </c>
       <c r="R20" t="n">
-        <v>245</v>
+        <v>-0.33</v>
       </c>
       <c r="S20" t="n">
-        <v>246</v>
+        <v>1.02</v>
       </c>
       <c r="T20" t="n">
-        <v>249</v>
+        <v>1.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Earnings Per Share, Diluted</t>
+          <t>Number of Shares - Diluted</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.52</v>
+        <v>212</v>
       </c>
       <c r="C21" t="n">
-        <v>0.6899999999999999</v>
+        <v>208</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.62</v>
+        <v>195</v>
       </c>
       <c r="E21" t="n">
-        <v>3.61</v>
+        <v>196</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.79</v>
+        <v>203</v>
       </c>
       <c r="G21" t="n">
-        <v>3.37</v>
+        <v>207</v>
       </c>
       <c r="H21" t="n">
-        <v>2.31</v>
+        <v>214</v>
       </c>
       <c r="I21" t="n">
-        <v>1.41</v>
+        <v>214</v>
       </c>
       <c r="J21" t="n">
-        <v>1.25</v>
+        <v>232</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>232</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>235</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>237</v>
       </c>
       <c r="O21" t="n">
-        <v>6.6</v>
+        <v>242</v>
       </c>
       <c r="P21" t="n">
-        <v>4.4</v>
+        <v>245</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>245</v>
       </c>
       <c r="R21" t="n">
-        <v>1.02</v>
+        <v>245</v>
       </c>
       <c r="S21" t="n">
-        <v>1.27</v>
+        <v>245</v>
       </c>
       <c r="T21" t="n">
-        <v>0.49</v>
+        <v>246</v>
+      </c>
+      <c r="U21" t="n">
+        <v>249</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Asset Impairment Charges</t>
+          <t>Earnings Per Share, Diluted</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="C22" t="n">
-        <v>0</v>
+        <v>0.52</v>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-0.62</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="G22" t="n">
-        <v>15</v>
+        <v>-3.79</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>3.37</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="L22" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
@@ -4713,89 +4911,95 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>306</v>
+        <v>6.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R22" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.27</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Income (Loss) from Equity Method Investments</t>
+          <t>Asset Impairment Charges</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>0</v>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I23" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>4</v>
+        <v>43</v>
       </c>
       <c r="N23" t="n">
-        <v>-15</v>
+        <v>155</v>
       </c>
       <c r="O23" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-6</v>
+        <v>306</v>
       </c>
       <c r="R23" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="T23" t="n">
-        <v>-11</v>
+        <v>0</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) on Extinguishment of Debt</t>
+          <t>Income (Loss) from Equity Method Investments</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -4805,55 +5009,58 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-10</v>
+        <v>1</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G24" t="n">
-        <v>-202</v>
+        <v>6</v>
       </c>
       <c r="H24" t="n">
-        <v>-58</v>
+        <v>4</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="N24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O24" t="n">
-        <v>-57</v>
+        <v>-15</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>12</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-11</v>
       </c>
     </row>
     <row r="25">
@@ -4893,30 +5100,33 @@
         <v>0</v>
       </c>
       <c r="L25" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" t="n">
         <v>52</v>
       </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
         <v>26</v>
       </c>
-      <c r="N25" t="n">
+      <c r="O25" t="n">
         <v>25</v>
       </c>
-      <c r="O25" t="n">
+      <c r="P25" t="n">
         <v>64</v>
       </c>
-      <c r="P25" t="n">
+      <c r="Q25" t="n">
         <v>40</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="R25" t="n">
         <v>611</v>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
       <c r="S25" t="n">
         <v>0</v>
       </c>
       <c r="T25" t="n">
+        <v>0</v>
+      </c>
+      <c r="U25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -4975,12 +5185,15 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
         <v>1</v>
       </c>
-      <c r="S26" t="n">
+      <c r="T26" t="n">
         <v>2</v>
       </c>
-      <c r="T26" t="n">
+      <c r="U26" t="n">
         <v>3</v>
       </c>
     </row>
@@ -4991,60 +5204,63 @@
         </is>
       </c>
       <c r="B27" t="n">
+        <v>506</v>
+      </c>
+      <c r="C27" t="n">
         <v>125</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>152</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>-104</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
         <v>750</v>
       </c>
-      <c r="F27" t="n">
+      <c r="G27" t="n">
         <v>-767</v>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>738</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>511</v>
       </c>
-      <c r="I27" t="n">
+      <c r="J27" t="n">
         <v>343</v>
       </c>
-      <c r="J27" t="n">
+      <c r="K27" t="n">
         <v>308</v>
       </c>
-      <c r="K27" t="n">
+      <c r="L27" t="n">
         <v>-1335</v>
       </c>
-      <c r="L27" t="n">
+      <c r="M27" t="n">
         <v>67</v>
       </c>
-      <c r="M27" t="n">
+      <c r="N27" t="n">
         <v>513</v>
       </c>
-      <c r="N27" t="n">
+      <c r="O27" t="n">
         <v>1736</v>
       </c>
-      <c r="O27" t="n">
+      <c r="P27" t="n">
         <v>1618</v>
       </c>
-      <c r="P27" t="n">
+      <c r="Q27" t="n">
         <v>1078</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="R27" t="n">
         <v>-82</v>
       </c>
-      <c r="R27" t="n">
+      <c r="S27" t="n">
         <v>249</v>
       </c>
-      <c r="S27" t="n">
+      <c r="T27" t="n">
         <v>313</v>
       </c>
-      <c r="T27" t="n">
+      <c r="U27" t="n">
         <v>121</v>
       </c>
     </row>
@@ -5059,65 +5275,68 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T58"/>
+  <dimension ref="A1:U59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="C1" s="1" t="n">
         <v>46112</v>
       </c>
-      <c r="C1" s="1" t="n">
+      <c r="D1" s="1" t="n">
         <v>45930</v>
       </c>
-      <c r="D1" s="1" t="n">
+      <c r="E1" s="1" t="n">
         <v>45838</v>
       </c>
-      <c r="E1" s="1" t="n">
+      <c r="F1" s="1" t="n">
         <v>45747</v>
       </c>
-      <c r="F1" s="1" t="n">
+      <c r="G1" s="1" t="n">
         <v>45565</v>
       </c>
-      <c r="G1" s="1" t="n">
+      <c r="H1" s="1" t="n">
         <v>45473</v>
       </c>
-      <c r="H1" s="1" t="n">
+      <c r="I1" s="1" t="n">
         <v>45382</v>
       </c>
-      <c r="I1" s="1" t="n">
+      <c r="J1" s="1" t="n">
         <v>45199</v>
       </c>
-      <c r="J1" s="1" t="n">
+      <c r="K1" s="1" t="n">
         <v>45107</v>
       </c>
-      <c r="K1" s="1" t="n">
+      <c r="L1" s="1" t="n">
         <v>45016</v>
       </c>
-      <c r="L1" s="1" t="n">
+      <c r="M1" s="1" t="n">
         <v>44834</v>
       </c>
-      <c r="M1" s="1" t="n">
+      <c r="N1" s="1" t="n">
         <v>44742</v>
       </c>
-      <c r="N1" s="1" t="n">
+      <c r="O1" s="1" t="n">
         <v>44651</v>
       </c>
-      <c r="O1" s="1" t="n">
+      <c r="P1" s="1" t="n">
         <v>44469</v>
       </c>
-      <c r="P1" s="1" t="n">
+      <c r="Q1" s="1" t="n">
         <v>44377</v>
       </c>
-      <c r="Q1" s="1" t="n">
+      <c r="R1" s="1" t="n">
         <v>44286</v>
       </c>
-      <c r="R1" s="1" t="n">
+      <c r="S1" s="1" t="n">
         <v>44104</v>
       </c>
-      <c r="S1" s="1" t="n">
+      <c r="T1" s="1" t="n">
         <v>44012</v>
       </c>
-      <c r="T1" s="1" t="n">
+      <c r="U1" s="1" t="n">
         <v>43921</v>
       </c>
     </row>
@@ -5128,60 +5347,63 @@
         </is>
       </c>
       <c r="B2" t="n">
+        <v>631</v>
+      </c>
+      <c r="C2" t="n">
         <v>125</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>798</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>646</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>750</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>482</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>1249</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>511</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>-684</v>
       </c>
-      <c r="J2" t="n">
+      <c r="K2" t="n">
         <v>-1027</v>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>-1335</v>
       </c>
-      <c r="L2" t="n">
+      <c r="M2" t="n">
         <v>2316</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>2249</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>1736</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>2614</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>996</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="R2" t="n">
         <v>-82</v>
       </c>
-      <c r="R2" t="n">
+      <c r="S2" t="n">
         <v>683</v>
       </c>
-      <c r="S2" t="n">
+      <c r="T2" t="n">
         <v>434</v>
       </c>
-      <c r="T2" t="n">
+      <c r="U2" t="n">
         <v>121</v>
       </c>
     </row>
@@ -5192,60 +5414,63 @@
         </is>
       </c>
       <c r="B3" t="n">
+        <v>602</v>
+      </c>
+      <c r="C3" t="n">
         <v>277</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>667</v>
       </c>
-      <c r="D3" t="n">
+      <c r="E3" t="n">
         <v>444</v>
       </c>
-      <c r="E3" t="n">
+      <c r="F3" t="n">
         <v>218</v>
       </c>
-      <c r="F3" t="n">
+      <c r="G3" t="n">
         <v>814</v>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>553</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>268</v>
       </c>
-      <c r="I3" t="n">
+      <c r="J3" t="n">
         <v>813</v>
       </c>
-      <c r="J3" t="n">
+      <c r="K3" t="n">
         <v>505</v>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>190</v>
       </c>
-      <c r="L3" t="n">
+      <c r="M3" t="n">
         <v>485</v>
       </c>
-      <c r="M3" t="n">
+      <c r="N3" t="n">
         <v>340</v>
       </c>
-      <c r="N3" t="n">
+      <c r="O3" t="n">
         <v>183</v>
       </c>
-      <c r="O3" t="n">
+      <c r="P3" t="n">
         <v>569</v>
       </c>
-      <c r="P3" t="n">
+      <c r="Q3" t="n">
         <v>370</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="R3" t="n">
         <v>317</v>
       </c>
-      <c r="R3" t="n">
+      <c r="S3" t="n">
         <v>318</v>
       </c>
-      <c r="S3" t="n">
+      <c r="T3" t="n">
         <v>219</v>
       </c>
-      <c r="T3" t="n">
+      <c r="U3" t="n">
         <v>109</v>
       </c>
     </row>
@@ -5256,23 +5481,23 @@
         </is>
       </c>
       <c r="B4" t="n">
+        <v>324</v>
+      </c>
+      <c r="C4" t="n">
         <v>155</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>363</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>226</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
         <v>108</v>
       </c>
-      <c r="F4" t="n">
+      <c r="G4" t="n">
         <v>231</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
       <c r="H4" t="n">
         <v>0</v>
       </c>
@@ -5310,6 +5535,9 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5320,11 +5548,11 @@
         </is>
       </c>
       <c r="B5" t="n">
+        <v>17</v>
+      </c>
+      <c r="C5" t="n">
         <v>7</v>
       </c>
-      <c r="C5" t="n">
-        <v>0</v>
-      </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
@@ -5374,6 +5602,9 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5384,60 +5615,63 @@
         </is>
       </c>
       <c r="B6" t="n">
+        <v>104</v>
+      </c>
+      <c r="C6" t="n">
         <v>59</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>201</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>113</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
         <v>56</v>
       </c>
-      <c r="F6" t="n">
+      <c r="G6" t="n">
         <v>228</v>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>133</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>75</v>
       </c>
-      <c r="I6" t="n">
+      <c r="J6" t="n">
         <v>165</v>
       </c>
-      <c r="J6" t="n">
+      <c r="K6" t="n">
         <v>80</v>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>35</v>
       </c>
-      <c r="L6" t="n">
+      <c r="M6" t="n">
         <v>103</v>
       </c>
-      <c r="M6" t="n">
+      <c r="N6" t="n">
         <v>51</v>
       </c>
-      <c r="N6" t="n">
+      <c r="O6" t="n">
         <v>25</v>
       </c>
-      <c r="O6" t="n">
+      <c r="P6" t="n">
         <v>715</v>
       </c>
-      <c r="P6" t="n">
+      <c r="Q6" t="n">
         <v>651</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="R6" t="n">
         <v>611</v>
       </c>
-      <c r="R6" t="n">
+      <c r="S6" t="n">
         <v>74</v>
       </c>
-      <c r="S6" t="n">
+      <c r="T6" t="n">
         <v>48</v>
       </c>
-      <c r="T6" t="n">
+      <c r="U6" t="n">
         <v>24</v>
       </c>
     </row>
@@ -5448,113 +5682,116 @@
         </is>
       </c>
       <c r="B7" t="n">
+        <v>10</v>
+      </c>
+      <c r="C7" t="n">
         <v>5</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>24</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>13</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
         <v>6</v>
       </c>
-      <c r="F7" t="n">
+      <c r="G7" t="n">
         <v>32</v>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>21</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>11</v>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>42</v>
       </c>
-      <c r="J7" t="n">
+      <c r="K7" t="n">
         <v>31</v>
       </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
         <v>20</v>
       </c>
-      <c r="L7" t="n">
+      <c r="M7" t="n">
         <v>17</v>
       </c>
-      <c r="M7" t="n">
+      <c r="N7" t="n">
         <v>11</v>
       </c>
-      <c r="N7" t="n">
+      <c r="O7" t="n">
         <v>6</v>
       </c>
-      <c r="O7" t="n">
+      <c r="P7" t="n">
         <v>30</v>
       </c>
-      <c r="P7" t="n">
+      <c r="Q7" t="n">
         <v>20</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="R7" t="n">
         <v>11</v>
       </c>
-      <c r="R7" t="n">
+      <c r="S7" t="n">
         <v>23</v>
       </c>
-      <c r="S7" t="n">
+      <c r="T7" t="n">
         <v>12</v>
       </c>
-      <c r="T7" t="n">
+      <c r="U7" t="n">
         <v>6</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Amortization Of Intangibles In The Money Contracts And Retirement Of RECs</t>
+          <t>Gain (Loss) on Extinguishment of Debt</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>36</v>
+        <v>9</v>
       </c>
       <c r="C8" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>44</v>
+        <v>10</v>
       </c>
       <c r="F8" t="n">
-        <v>83</v>
+        <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>73</v>
+        <v>260</v>
       </c>
       <c r="H8" t="n">
-        <v>78</v>
+        <v>260</v>
       </c>
       <c r="I8" t="n">
-        <v>111</v>
+        <v>58</v>
       </c>
       <c r="J8" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="L8" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>128</v>
+        <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
-        <v>111</v>
+        <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>108</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -5566,468 +5803,492 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>Share-based Payment Arrangement, Noncash Expense</t>
+          <t>Amortization Of Intangibles In The Money Contracts And Retirement Of RECs</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C9" t="n">
+        <v>36</v>
+      </c>
+      <c r="D9" t="n">
+        <v>75</v>
+      </c>
+      <c r="E9" t="n">
+        <v>51</v>
+      </c>
+      <c r="F9" t="n">
+        <v>44</v>
+      </c>
+      <c r="G9" t="n">
         <v>83</v>
       </c>
-      <c r="D9" t="n">
-        <v>62</v>
-      </c>
-      <c r="E9" t="n">
-        <v>29</v>
-      </c>
-      <c r="F9" t="n">
-        <v>82</v>
-      </c>
-      <c r="G9" t="n">
-        <v>57</v>
-      </c>
       <c r="H9" t="n">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="I9" t="n">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="J9" t="n">
-        <v>61</v>
+        <v>111</v>
       </c>
       <c r="K9" t="n">
-        <v>30</v>
+        <v>112</v>
       </c>
       <c r="L9" t="n">
-        <v>21</v>
+        <v>119</v>
       </c>
       <c r="M9" t="n">
-        <v>14</v>
+        <v>122</v>
       </c>
       <c r="N9" t="n">
-        <v>6</v>
+        <v>128</v>
       </c>
       <c r="O9" t="n">
-        <v>16</v>
+        <v>147</v>
       </c>
       <c r="P9" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>108</v>
       </c>
       <c r="R9" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>5</v>
+        <v>0</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) On Sale And Disposition Of Assets</t>
+          <t>Share-based Payment Arrangement, Noncash Expense</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>72</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D10" t="n">
+        <v>83</v>
+      </c>
+      <c r="E10" t="n">
+        <v>62</v>
+      </c>
+      <c r="F10" t="n">
+        <v>29</v>
+      </c>
+      <c r="G10" t="n">
+        <v>82</v>
+      </c>
+      <c r="H10" t="n">
+        <v>57</v>
+      </c>
+      <c r="I10" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" t="n">
+        <v>87</v>
+      </c>
+      <c r="K10" t="n">
+        <v>61</v>
+      </c>
+      <c r="L10" t="n">
+        <v>30</v>
+      </c>
+      <c r="M10" t="n">
+        <v>21</v>
+      </c>
+      <c r="N10" t="n">
+        <v>14</v>
+      </c>
+      <c r="O10" t="n">
+        <v>6</v>
+      </c>
+      <c r="P10" t="n">
+        <v>16</v>
+      </c>
+      <c r="Q10" t="n">
         <v>10</v>
       </c>
-      <c r="E10" t="n">
-        <v>8</v>
-      </c>
-      <c r="F10" t="n">
-        <v>-197</v>
-      </c>
-      <c r="G10" t="n">
-        <v>8</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>-187</v>
-      </c>
-      <c r="J10" t="n">
-        <v>-187</v>
-      </c>
-      <c r="K10" t="n">
-        <v>-187</v>
-      </c>
-      <c r="L10" t="n">
-        <v>-82</v>
-      </c>
-      <c r="M10" t="n">
-        <v>-46</v>
-      </c>
-      <c r="N10" t="n">
-        <v>-6</v>
-      </c>
-      <c r="O10" t="n">
-        <v>-29</v>
-      </c>
-      <c r="P10" t="n">
-        <v>-25</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>-18</v>
-      </c>
       <c r="R10" t="n">
-        <v>-22</v>
+        <v>4</v>
       </c>
       <c r="S10" t="n">
-        <v>-15</v>
+        <v>17</v>
       </c>
       <c r="T10" t="n">
-        <v>-14</v>
+        <v>12</v>
+      </c>
+      <c r="U10" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) on Disposition of Property Plant Equipment</t>
+          <t>Gain (Loss) On Sale And Disposition Of Assets</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0</v>
+        <v>-38</v>
       </c>
       <c r="C11" t="n">
-        <v>-100</v>
+        <v>3</v>
       </c>
       <c r="D11" t="n">
-        <v>-100</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
-        <v>-100</v>
+        <v>10</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-197</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-187</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>-82</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>-46</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-22</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-15</v>
+      </c>
+      <c r="U11" t="n">
+        <v>-14</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Derivative Assets and Liabilities</t>
+          <t>Gain (Loss) on Disposition of Property Plant Equipment</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>447</v>
+        <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>18</v>
+        <v>-100</v>
       </c>
       <c r="E12" t="n">
-        <v>-320</v>
+        <v>-100</v>
       </c>
       <c r="F12" t="n">
-        <v>268</v>
+        <v>-100</v>
       </c>
       <c r="G12" t="n">
-        <v>-1384</v>
+        <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-535</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1553</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1515</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>1599</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-4480</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-3918</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-2816</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>-4419</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>-2430</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-902</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-7</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>-131</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>-46</v>
+        <v>0</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Income Taxes</t>
+          <t>Increase (Decrease) in Derivative Assets and Liabilities</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>-56</v>
+        <v>-61</v>
       </c>
       <c r="C13" t="n">
-        <v>209</v>
+        <v>190</v>
       </c>
       <c r="D13" t="n">
-        <v>126</v>
+        <v>447</v>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>18</v>
       </c>
       <c r="F13" t="n">
-        <v>134</v>
+        <v>-320</v>
       </c>
       <c r="G13" t="n">
-        <v>390</v>
+        <v>268</v>
       </c>
       <c r="H13" t="n">
-        <v>139</v>
+        <v>-1384</v>
       </c>
       <c r="I13" t="n">
-        <v>-225</v>
+        <v>-535</v>
       </c>
       <c r="J13" t="n">
-        <v>-282</v>
+        <v>1553</v>
       </c>
       <c r="K13" t="n">
-        <v>-338</v>
+        <v>1515</v>
       </c>
       <c r="L13" t="n">
-        <v>688</v>
+        <v>1599</v>
       </c>
       <c r="M13" t="n">
-        <v>672</v>
+        <v>-4480</v>
       </c>
       <c r="N13" t="n">
-        <v>527</v>
+        <v>-3918</v>
       </c>
       <c r="O13" t="n">
-        <v>782</v>
+        <v>-2816</v>
       </c>
       <c r="P13" t="n">
-        <v>257</v>
+        <v>-4419</v>
       </c>
       <c r="Q13" t="n">
-        <v>-71</v>
+        <v>-2430</v>
       </c>
       <c r="R13" t="n">
-        <v>202</v>
+        <v>-902</v>
       </c>
       <c r="S13" t="n">
-        <v>116</v>
+        <v>-7</v>
       </c>
       <c r="T13" t="n">
-        <v>19</v>
+        <v>-131</v>
+      </c>
+      <c r="U13" t="n">
+        <v>-46</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Changes In Collateral Deposits Supporting Energy Risk Management Activities</t>
+          <t>Increase (Decrease) in Income Taxes</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>-142</v>
+        <v>-33</v>
       </c>
       <c r="C14" t="n">
-        <v>76</v>
+        <v>-56</v>
       </c>
       <c r="D14" t="n">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E14" t="n">
-        <v>623</v>
+        <v>126</v>
       </c>
       <c r="F14" t="n">
-        <v>-80</v>
+        <v>143</v>
       </c>
       <c r="G14" t="n">
-        <v>660</v>
+        <v>134</v>
       </c>
       <c r="H14" t="n">
-        <v>289</v>
+        <v>390</v>
       </c>
       <c r="I14" t="n">
-        <v>-1188</v>
+        <v>139</v>
       </c>
       <c r="J14" t="n">
-        <v>-1355</v>
+        <v>-225</v>
       </c>
       <c r="K14" t="n">
-        <v>-1412</v>
+        <v>-282</v>
       </c>
       <c r="L14" t="n">
-        <v>2321</v>
+        <v>-338</v>
       </c>
       <c r="M14" t="n">
-        <v>3121</v>
+        <v>688</v>
       </c>
       <c r="N14" t="n">
-        <v>2007</v>
+        <v>672</v>
       </c>
       <c r="O14" t="n">
-        <v>1970</v>
+        <v>527</v>
       </c>
       <c r="P14" t="n">
-        <v>696</v>
+        <v>782</v>
       </c>
       <c r="Q14" t="n">
-        <v>1</v>
+        <v>257</v>
       </c>
       <c r="R14" t="n">
-        <v>96</v>
+        <v>-71</v>
       </c>
       <c r="S14" t="n">
-        <v>58</v>
+        <v>202</v>
       </c>
       <c r="T14" t="n">
-        <v>9</v>
+        <v>116</v>
+      </c>
+      <c r="U14" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accounts Receivable</t>
+          <t>Changes In Collateral Deposits Supporting Energy Risk Management Activities</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>809</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>0</v>
+        <v>-142</v>
       </c>
       <c r="D15" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>197</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>623</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>-80</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>289</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-1188</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>-1355</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-1412</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>2321</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>3121</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>2007</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1970</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>696</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>58</v>
+      </c>
+      <c r="U15" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Inventories</t>
+          <t>Increase (Decrease) in Accounts Receivable</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-29</v>
+        <v>910</v>
       </c>
       <c r="C16" t="n">
-        <v>0</v>
+        <v>809</v>
       </c>
       <c r="D16" t="n">
         <v>0</v>
@@ -6078,20 +6339,23 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Prepaid Expense and Other Assets</t>
+          <t>Increase (Decrease) in Inventories</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>-196</v>
+        <v>-156</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>-29</v>
       </c>
       <c r="D17" t="n">
         <v>0</v>
@@ -6142,20 +6406,23 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Accounts Payable</t>
+          <t>Increase (Decrease) in Prepaid Expense and Other Assets</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-910</v>
+        <v>-441</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>-196</v>
       </c>
       <c r="D18" t="n">
         <v>0</v>
@@ -6206,20 +6473,23 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>nrg_IncreaseDecreaseAccruedExpensesAndOtherCurrentLiabilitiesOperating</t>
+          <t>Increase (Decrease) in Accounts Payable</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>-315</v>
+        <v>-780</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>-910</v>
       </c>
       <c r="D19" t="n">
         <v>0</v>
@@ -6270,495 +6540,519 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
+          <t>nrg_IncreaseDecreaseAccruedExpensesAndOtherCurrentLiabilitiesOperating</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>-228</v>
+        <v>-164</v>
       </c>
       <c r="C20" t="n">
-        <v>-1090</v>
+        <v>-315</v>
       </c>
       <c r="D20" t="n">
-        <v>-529</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>-699</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-1021</v>
+        <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>-711</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>-668</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-985</v>
+        <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>-505</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>-317</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-711</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-332</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>-171</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-973</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>-665</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-843</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>-237</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>-199</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>-99</v>
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Operating Activities</t>
+          <t>Increase (Decrease) in Other Operating Assets and Liabilities, Net</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>-169</v>
+        <v>-119</v>
       </c>
       <c r="C21" t="n">
-        <v>1790</v>
+        <v>-228</v>
       </c>
       <c r="D21" t="n">
-        <v>1306</v>
+        <v>-1090</v>
       </c>
       <c r="E21" t="n">
-        <v>855</v>
+        <v>-529</v>
       </c>
       <c r="F21" t="n">
-        <v>1354</v>
+        <v>-699</v>
       </c>
       <c r="G21" t="n">
-        <v>1323</v>
+        <v>-1021</v>
       </c>
       <c r="H21" t="n">
-        <v>267</v>
+        <v>-711</v>
       </c>
       <c r="I21" t="n">
-        <v>-462</v>
+        <v>-668</v>
       </c>
       <c r="J21" t="n">
-        <v>-1028</v>
+        <v>-985</v>
       </c>
       <c r="K21" t="n">
-        <v>-1598</v>
+        <v>-505</v>
       </c>
       <c r="L21" t="n">
-        <v>1758</v>
+        <v>-317</v>
       </c>
       <c r="M21" t="n">
-        <v>3189</v>
+        <v>-711</v>
       </c>
       <c r="N21" t="n">
-        <v>1676</v>
+        <v>-332</v>
       </c>
       <c r="O21" t="n">
-        <v>1855</v>
+        <v>-171</v>
       </c>
       <c r="P21" t="n">
-        <v>377</v>
+        <v>-973</v>
       </c>
       <c r="Q21" t="n">
-        <v>-917</v>
+        <v>-665</v>
       </c>
       <c r="R21" t="n">
-        <v>1386</v>
+        <v>-843</v>
       </c>
       <c r="S21" t="n">
-        <v>692</v>
+        <v>-237</v>
       </c>
       <c r="T21" t="n">
-        <v>208</v>
+        <v>-199</v>
+      </c>
+      <c r="U21" t="n">
+        <v>-99</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Property, Plant, and Equipment</t>
+          <t>Net Cash Provided by (Used in) Operating Activities</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>-317</v>
+        <v>948</v>
       </c>
       <c r="C22" t="n">
-        <v>-849</v>
+        <v>-169</v>
       </c>
       <c r="D22" t="n">
-        <v>-595</v>
+        <v>1790</v>
       </c>
       <c r="E22" t="n">
-        <v>-217</v>
+        <v>1306</v>
       </c>
       <c r="F22" t="n">
-        <v>-286</v>
+        <v>855</v>
       </c>
       <c r="G22" t="n">
-        <v>-172</v>
+        <v>1354</v>
       </c>
       <c r="H22" t="n">
-        <v>-69</v>
+        <v>1323</v>
       </c>
       <c r="I22" t="n">
-        <v>-493</v>
+        <v>267</v>
       </c>
       <c r="J22" t="n">
-        <v>-324</v>
+        <v>-462</v>
       </c>
       <c r="K22" t="n">
-        <v>-142</v>
+        <v>-1028</v>
       </c>
       <c r="L22" t="n">
-        <v>-250</v>
+        <v>-1598</v>
       </c>
       <c r="M22" t="n">
-        <v>-150</v>
+        <v>1758</v>
       </c>
       <c r="N22" t="n">
-        <v>-60</v>
+        <v>3189</v>
       </c>
       <c r="O22" t="n">
-        <v>-219</v>
+        <v>1676</v>
       </c>
       <c r="P22" t="n">
-        <v>-143</v>
+        <v>1855</v>
       </c>
       <c r="Q22" t="n">
-        <v>-63</v>
+        <v>377</v>
       </c>
       <c r="R22" t="n">
-        <v>-167</v>
+        <v>-917</v>
       </c>
       <c r="S22" t="n">
-        <v>-116</v>
+        <v>1386</v>
       </c>
       <c r="T22" t="n">
-        <v>-66</v>
+        <v>692</v>
+      </c>
+      <c r="U22" t="n">
+        <v>208</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sales of Assets, Investing Activities</t>
+          <t>Payments to Acquire Property, Plant, and Equipment</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>-655</v>
       </c>
       <c r="C23" t="n">
-        <v>6</v>
+        <v>-317</v>
       </c>
       <c r="D23" t="n">
-        <v>6</v>
+        <v>-849</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>-595</v>
       </c>
       <c r="F23" t="n">
-        <v>495</v>
+        <v>-217</v>
       </c>
       <c r="G23" t="n">
-        <v>11</v>
+        <v>-286</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>-172</v>
       </c>
       <c r="I23" t="n">
-        <v>229</v>
+        <v>-69</v>
       </c>
       <c r="J23" t="n">
-        <v>229</v>
+        <v>-493</v>
       </c>
       <c r="K23" t="n">
-        <v>219</v>
+        <v>-324</v>
       </c>
       <c r="L23" t="n">
-        <v>107</v>
+        <v>-142</v>
       </c>
       <c r="M23" t="n">
-        <v>96</v>
+        <v>-250</v>
       </c>
       <c r="N23" t="n">
-        <v>14</v>
+        <v>-150</v>
       </c>
       <c r="O23" t="n">
-        <v>198</v>
+        <v>-60</v>
       </c>
       <c r="P23" t="n">
-        <v>198</v>
+        <v>-219</v>
       </c>
       <c r="Q23" t="n">
-        <v>197</v>
+        <v>-143</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>-63</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>-167</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-116</v>
+      </c>
+      <c r="U23" t="n">
+        <v>-66</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>Payments For Proceeds From Intangible Assets</t>
+          <t>Proceeds from Sales of Assets, Investing Activities</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C24" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>-7</v>
+        <v>6</v>
       </c>
       <c r="E24" t="n">
-        <v>-3</v>
+        <v>6</v>
       </c>
       <c r="F24" t="n">
-        <v>-16</v>
+        <v>6</v>
       </c>
       <c r="G24" t="n">
-        <v>-11</v>
+        <v>495</v>
       </c>
       <c r="H24" t="n">
-        <v>-7</v>
+        <v>11</v>
       </c>
       <c r="I24" t="n">
-        <v>-25</v>
+        <v>3</v>
       </c>
       <c r="J24" t="n">
-        <v>-25</v>
+        <v>229</v>
       </c>
       <c r="K24" t="n">
-        <v>-18</v>
+        <v>229</v>
       </c>
       <c r="L24" t="n">
-        <v>-4</v>
+        <v>219</v>
       </c>
       <c r="M24" t="n">
-        <v>-19</v>
+        <v>107</v>
       </c>
       <c r="N24" t="n">
-        <v>-18</v>
+        <v>96</v>
       </c>
       <c r="O24" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="P24" t="n">
-        <v>1</v>
+        <v>198</v>
       </c>
       <c r="Q24" t="n">
-        <v>-5</v>
+        <v>198</v>
       </c>
       <c r="R24" t="n">
-        <v>-15</v>
+        <v>197</v>
       </c>
       <c r="S24" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>-8</v>
+        <v>0</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Proceeds From Insurance Recovery Property Plant And Equipment, Net</t>
+          <t>Payments For Proceeds From Intangible Assets</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>-41</v>
       </c>
       <c r="C25" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>100</v>
+        <v>-6</v>
       </c>
       <c r="E25" t="n">
-        <v>100</v>
+        <v>-7</v>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>-3</v>
       </c>
       <c r="G25" t="n">
-        <v>3</v>
+        <v>-16</v>
       </c>
       <c r="H25" t="n">
-        <v>3</v>
+        <v>-11</v>
       </c>
       <c r="I25" t="n">
-        <v>173</v>
+        <v>-7</v>
       </c>
       <c r="J25" t="n">
-        <v>121</v>
+        <v>-25</v>
       </c>
       <c r="K25" t="n">
-        <v>71</v>
+        <v>-25</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>-19</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-4</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-8</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Investing Activities</t>
+          <t>Proceeds from Sale of Intangible Assets</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-7072</v>
+        <v>44</v>
       </c>
       <c r="C26" t="n">
-        <v>-1340</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>-1082</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>-134</v>
+        <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>-201</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-92</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>-2631</v>
+        <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>-2502</v>
+        <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>-2350</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
-        <v>-205</v>
+        <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>-119</v>
+        <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
-        <v>-3585</v>
+        <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>-3492</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>-3364</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>-484</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
-        <v>-145</v>
+        <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>-68</v>
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
+          <t>Proceeds From Insurance Recovery Property Plant And Equipment, Net</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-79</v>
+        <v>0</v>
       </c>
       <c r="C27" t="n">
-        <v>-86</v>
+        <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>-77</v>
+        <v>100</v>
       </c>
       <c r="E27" t="n">
-        <v>-40</v>
+        <v>100</v>
       </c>
       <c r="F27" t="n">
-        <v>-45</v>
+        <v>100</v>
       </c>
       <c r="G27" t="n">
-        <v>-35</v>
+        <v>3</v>
       </c>
       <c r="H27" t="n">
-        <v>-23</v>
+        <v>3</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>173</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>71</v>
       </c>
       <c r="M27" t="n">
         <v>0</v>
@@ -6782,303 +7076,318 @@
         <v>0</v>
       </c>
       <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Payments for Repurchase of Common Stock</t>
+          <t>Net Cash Provided by (Used in) Investing Activities</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-481</v>
+        <v>-7709</v>
       </c>
       <c r="C28" t="n">
-        <v>-958</v>
+        <v>-7072</v>
       </c>
       <c r="D28" t="n">
-        <v>-603</v>
+        <v>-1340</v>
       </c>
       <c r="E28" t="n">
-        <v>-314</v>
+        <v>-1082</v>
       </c>
       <c r="F28" t="n">
-        <v>-316</v>
+        <v>-134</v>
       </c>
       <c r="G28" t="n">
-        <v>-90</v>
+        <v>163</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>-201</v>
       </c>
       <c r="I28" t="n">
-        <v>-69</v>
+        <v>-92</v>
       </c>
       <c r="J28" t="n">
-        <v>-16</v>
+        <v>-2631</v>
       </c>
       <c r="K28" t="n">
-        <v>-8</v>
+        <v>-2502</v>
       </c>
       <c r="L28" t="n">
+        <v>-2350</v>
+      </c>
+      <c r="M28" t="n">
+        <v>-205</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-119</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-80</v>
+      </c>
+      <c r="P28" t="n">
+        <v>-3585</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-3492</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-3364</v>
+      </c>
+      <c r="S28" t="n">
         <v>-484</v>
       </c>
-      <c r="M28" t="n">
-        <v>-366</v>
-      </c>
-      <c r="N28" t="n">
-        <v>-188</v>
-      </c>
-      <c r="O28" t="n">
-        <v>-9</v>
-      </c>
-      <c r="P28" t="n">
-        <v>-9</v>
-      </c>
-      <c r="Q28" t="n">
-        <v>-9</v>
-      </c>
-      <c r="R28" t="n">
-        <v>-229</v>
-      </c>
-      <c r="S28" t="n">
-        <v>-229</v>
-      </c>
       <c r="T28" t="n">
-        <v>-179</v>
+        <v>-145</v>
+      </c>
+      <c r="U28" t="n">
+        <v>-68</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Payments of Dividends</t>
+          <t>Payment, Tax Withholding, Share-based Payment Arrangement</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-135</v>
+        <v>-99</v>
       </c>
       <c r="C29" t="n">
-        <v>-326</v>
+        <v>-79</v>
       </c>
       <c r="D29" t="n">
-        <v>-207</v>
+        <v>-86</v>
       </c>
       <c r="E29" t="n">
-        <v>-121</v>
+        <v>-77</v>
       </c>
       <c r="F29" t="n">
-        <v>-322</v>
+        <v>-40</v>
       </c>
       <c r="G29" t="n">
-        <v>-204</v>
+        <v>-45</v>
       </c>
       <c r="H29" t="n">
-        <v>-118</v>
+        <v>-35</v>
       </c>
       <c r="I29" t="n">
-        <v>-295</v>
+        <v>-23</v>
       </c>
       <c r="J29" t="n">
-        <v>-174</v>
+        <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>-87</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
-        <v>-252</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>-168</v>
+        <v>0</v>
       </c>
       <c r="N29" t="n">
-        <v>-85</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
-        <v>-239</v>
+        <v>0</v>
       </c>
       <c r="P29" t="n">
-        <v>-159</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>-221</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
-        <v>-148</v>
+        <v>0</v>
       </c>
       <c r="T29" t="n">
-        <v>-74</v>
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Debt</t>
+          <t>Payments for Repurchase of Common Stock</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>57</v>
+        <v>-931</v>
       </c>
       <c r="C30" t="n">
-        <v>1375</v>
+        <v>-481</v>
       </c>
       <c r="D30" t="n">
-        <v>0</v>
+        <v>-958</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-603</v>
       </c>
       <c r="F30" t="n">
-        <v>875</v>
+        <v>-314</v>
       </c>
       <c r="G30" t="n">
-        <v>875</v>
+        <v>-316</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-90</v>
       </c>
       <c r="I30" t="n">
-        <v>731</v>
+        <v>0</v>
       </c>
       <c r="J30" t="n">
-        <v>731</v>
+        <v>-69</v>
       </c>
       <c r="K30" t="n">
-        <v>731</v>
+        <v>-16</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>-484</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-366</v>
       </c>
       <c r="O30" t="n">
-        <v>1100</v>
+        <v>-188</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="R30" t="n">
-        <v>59</v>
+        <v>-9</v>
       </c>
       <c r="S30" t="n">
-        <v>59</v>
+        <v>-229</v>
       </c>
       <c r="T30" t="n">
-        <v>59</v>
+        <v>-229</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-179</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Other Debt</t>
+          <t>Payments of Dividends</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-12</v>
+        <v>-235</v>
       </c>
       <c r="C31" t="n">
-        <v>-249</v>
+        <v>-135</v>
       </c>
       <c r="D31" t="n">
-        <v>-10</v>
+        <v>-326</v>
       </c>
       <c r="E31" t="n">
-        <v>-5</v>
+        <v>-207</v>
       </c>
       <c r="F31" t="n">
-        <v>-960</v>
+        <v>-121</v>
       </c>
       <c r="G31" t="n">
-        <v>-956</v>
+        <v>-322</v>
       </c>
       <c r="H31" t="n">
-        <v>-97</v>
+        <v>-204</v>
       </c>
       <c r="I31" t="n">
-        <v>-15</v>
+        <v>-118</v>
       </c>
       <c r="J31" t="n">
-        <v>-10</v>
+        <v>-295</v>
       </c>
       <c r="K31" t="n">
-        <v>-4</v>
+        <v>-174</v>
       </c>
       <c r="L31" t="n">
-        <v>-4</v>
+        <v>-87</v>
       </c>
       <c r="M31" t="n">
-        <v>-2</v>
+        <v>-252</v>
       </c>
       <c r="N31" t="n">
-        <v>-1</v>
+        <v>-168</v>
       </c>
       <c r="O31" t="n">
-        <v>-1360</v>
+        <v>-85</v>
       </c>
       <c r="P31" t="n">
-        <v>-4</v>
+        <v>-239</v>
       </c>
       <c r="Q31" t="n">
-        <v>-1</v>
+        <v>-159</v>
       </c>
       <c r="R31" t="n">
-        <v>-62</v>
+        <v>-80</v>
       </c>
       <c r="S31" t="n">
-        <v>-61</v>
+        <v>-221</v>
       </c>
       <c r="T31" t="n">
-        <v>-60</v>
+        <v>-148</v>
+      </c>
+      <c r="U31" t="n">
+        <v>-74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Payments of Debt Issuance Costs</t>
+          <t>Proceeds from Issuance of Debt</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-42</v>
+        <v>3652</v>
       </c>
       <c r="C32" t="n">
-        <v>-55</v>
+        <v>57</v>
       </c>
       <c r="D32" t="n">
-        <v>-31</v>
+        <v>1375</v>
       </c>
       <c r="E32" t="n">
-        <v>-3</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>-13</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>-12</v>
+        <v>875</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>875</v>
       </c>
       <c r="I32" t="n">
-        <v>-29</v>
+        <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>-22</v>
+        <v>731</v>
       </c>
       <c r="K32" t="n">
-        <v>-18</v>
+        <v>731</v>
       </c>
       <c r="L32" t="n">
-        <v>-1</v>
+        <v>731</v>
       </c>
       <c r="M32" t="n">
         <v>0</v>
@@ -7087,123 +7396,129 @@
         <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>-18</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
-        <v>-2</v>
+        <v>1100</v>
       </c>
       <c r="Q32" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>-1</v>
+        <v>59</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>59</v>
+      </c>
+      <c r="U32" t="n">
+        <v>59</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Derivative Instrument, Financing Activities</t>
+          <t>Repayments of Other Debt</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>19</v>
+        <v>-1619</v>
       </c>
       <c r="C33" t="n">
-        <v>51</v>
+        <v>-12</v>
       </c>
       <c r="D33" t="n">
-        <v>38</v>
+        <v>-249</v>
       </c>
       <c r="E33" t="n">
-        <v>25</v>
+        <v>-10</v>
       </c>
       <c r="F33" t="n">
+        <v>-5</v>
+      </c>
+      <c r="G33" t="n">
+        <v>-960</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-956</v>
+      </c>
+      <c r="I33" t="n">
+        <v>-97</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-15</v>
+      </c>
+      <c r="K33" t="n">
+        <v>-10</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="M33" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N33" t="n">
         <v>-2</v>
       </c>
-      <c r="G33" t="n">
-        <v>-12</v>
-      </c>
-      <c r="H33" t="n">
-        <v>8</v>
-      </c>
-      <c r="I33" t="n">
-        <v>332</v>
-      </c>
-      <c r="J33" t="n">
-        <v>318</v>
-      </c>
-      <c r="K33" t="n">
-        <v>336</v>
-      </c>
-      <c r="L33" t="n">
-        <v>1596</v>
-      </c>
-      <c r="M33" t="n">
-        <v>950</v>
-      </c>
-      <c r="N33" t="n">
-        <v>561</v>
-      </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>-1360</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-62</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-61</v>
+      </c>
+      <c r="U33" t="n">
+        <v>-60</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Long-term Lines of Credit</t>
+          <t>Payment for Debt Extinguishment or Debt Prepayment Cost</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>4850</v>
+        <v>-9</v>
       </c>
       <c r="C34" t="n">
-        <v>1575</v>
+        <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>865</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>625</v>
+        <v>-258</v>
       </c>
       <c r="H34" t="n">
-        <v>525</v>
+        <v>-257</v>
       </c>
       <c r="I34" t="n">
-        <v>3020</v>
+        <v>-58</v>
       </c>
       <c r="J34" t="n">
-        <v>1870</v>
+        <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>1050</v>
+        <v>0</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -7218,10 +7533,10 @@
         <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>-48</v>
       </c>
       <c r="Q34" t="n">
-        <v>825</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -7230,50 +7545,53 @@
         <v>0</v>
       </c>
       <c r="T34" t="n">
-        <v>552</v>
+        <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Repayments of Long-term Lines of Credit</t>
+          <t>Payments of Debt Issuance Costs</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1525</v>
+        <v>-84</v>
       </c>
       <c r="C35" t="n">
-        <v>-1575</v>
+        <v>-42</v>
       </c>
       <c r="D35" t="n">
-        <v>-730</v>
+        <v>-55</v>
       </c>
       <c r="E35" t="n">
-        <v>0</v>
+        <v>-31</v>
       </c>
       <c r="F35" t="n">
-        <v>-1050</v>
+        <v>-3</v>
       </c>
       <c r="G35" t="n">
-        <v>-625</v>
+        <v>-13</v>
       </c>
       <c r="H35" t="n">
-        <v>-525</v>
+        <v>-12</v>
       </c>
       <c r="I35" t="n">
-        <v>-3020</v>
+        <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>-1670</v>
+        <v>-29</v>
       </c>
       <c r="K35" t="n">
-        <v>-825</v>
+        <v>-22</v>
       </c>
       <c r="L35" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="M35" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -7282,480 +7600,504 @@
         <v>0</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>-18</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="R35" t="n">
-        <v>-83</v>
+        <v>-2</v>
       </c>
       <c r="S35" t="n">
-        <v>-83</v>
+        <v>-24</v>
       </c>
       <c r="T35" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>Net Cash Provided by (Used in) Financing Activities</t>
+          <t>Payments for (Proceeds from) Derivative Instrument, Financing Activities</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>2652</v>
+        <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-540</v>
+        <v>19</v>
       </c>
       <c r="D36" t="n">
-        <v>-755</v>
+        <v>51</v>
       </c>
       <c r="E36" t="n">
-        <v>-458</v>
+        <v>38</v>
       </c>
       <c r="F36" t="n">
-        <v>-1041</v>
+        <v>25</v>
       </c>
       <c r="G36" t="n">
-        <v>-691</v>
+        <v>-2</v>
       </c>
       <c r="H36" t="n">
-        <v>-288</v>
+        <v>-12</v>
       </c>
       <c r="I36" t="n">
-        <v>1590</v>
+        <v>8</v>
       </c>
       <c r="J36" t="n">
-        <v>2162</v>
+        <v>332</v>
       </c>
       <c r="K36" t="n">
-        <v>2536</v>
+        <v>318</v>
       </c>
       <c r="L36" t="n">
-        <v>855</v>
+        <v>336</v>
       </c>
       <c r="M36" t="n">
-        <v>414</v>
+        <v>1596</v>
       </c>
       <c r="N36" t="n">
-        <v>287</v>
+        <v>950</v>
       </c>
       <c r="O36" t="n">
-        <v>-177</v>
+        <v>561</v>
       </c>
       <c r="P36" t="n">
-        <v>93</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>924</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>-567</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
-        <v>-469</v>
+        <v>0</v>
       </c>
       <c r="T36" t="n">
-        <v>293</v>
+        <v>0</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
+          <t>Proceeds from Long-term Lines of Credit</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>2</v>
+        <v>8675</v>
       </c>
       <c r="C37" t="n">
-        <v>2</v>
+        <v>4850</v>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>1575</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>865</v>
       </c>
       <c r="F37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>1050</v>
       </c>
       <c r="H37" t="n">
-        <v>-2</v>
+        <v>625</v>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>525</v>
       </c>
       <c r="J37" t="n">
-        <v>3</v>
+        <v>3020</v>
       </c>
       <c r="K37" t="n">
-        <v>3</v>
+        <v>1870</v>
       </c>
       <c r="L37" t="n">
-        <v>-5</v>
+        <v>1050</v>
       </c>
       <c r="M37" t="n">
         <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
         <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>-2</v>
+        <v>825</v>
       </c>
       <c r="S37" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
+      </c>
+      <c r="U37" t="n">
+        <v>552</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
+          <t>Repayments of Long-term Lines of Credit</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-4587</v>
+        <v>-7226</v>
       </c>
       <c r="C38" t="n">
-        <v>-88</v>
+        <v>-1525</v>
       </c>
       <c r="D38" t="n">
-        <v>-530</v>
+        <v>-1575</v>
       </c>
       <c r="E38" t="n">
-        <v>265</v>
+        <v>-730</v>
       </c>
       <c r="F38" t="n">
-        <v>477</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>431</v>
+        <v>-1050</v>
       </c>
       <c r="H38" t="n">
-        <v>-115</v>
+        <v>-625</v>
       </c>
       <c r="I38" t="n">
-        <v>-1503</v>
+        <v>-525</v>
       </c>
       <c r="J38" t="n">
-        <v>-1365</v>
+        <v>-3020</v>
       </c>
       <c r="K38" t="n">
-        <v>-1409</v>
+        <v>-1670</v>
       </c>
       <c r="L38" t="n">
-        <v>2403</v>
+        <v>-825</v>
       </c>
       <c r="M38" t="n">
-        <v>3484</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
-        <v>1886</v>
+        <v>0</v>
       </c>
       <c r="O38" t="n">
-        <v>-1909</v>
+        <v>0</v>
       </c>
       <c r="P38" t="n">
-        <v>-3021</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>-3356</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>333</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
-        <v>77</v>
+        <v>-83</v>
       </c>
       <c r="T38" t="n">
-        <v>433</v>
+        <v>-83</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Including Disposal Group and Discontinued Operations</t>
+          <t>Net Cash Provided by (Used in) Financing Activities</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>4998</v>
+        <v>2140</v>
       </c>
       <c r="C39" t="n">
-        <v>1173</v>
+        <v>2652</v>
       </c>
       <c r="D39" t="n">
-        <v>1173</v>
+        <v>-540</v>
       </c>
       <c r="E39" t="n">
-        <v>1173</v>
+        <v>-755</v>
       </c>
       <c r="F39" t="n">
-        <v>649</v>
+        <v>-458</v>
       </c>
       <c r="G39" t="n">
-        <v>649</v>
+        <v>-1041</v>
       </c>
       <c r="H39" t="n">
-        <v>649</v>
+        <v>-691</v>
       </c>
       <c r="I39" t="n">
-        <v>2178</v>
+        <v>-288</v>
       </c>
       <c r="J39" t="n">
-        <v>2178</v>
+        <v>1590</v>
       </c>
       <c r="K39" t="n">
-        <v>2178</v>
+        <v>2162</v>
       </c>
       <c r="L39" t="n">
-        <v>1110</v>
+        <v>2536</v>
       </c>
       <c r="M39" t="n">
-        <v>1110</v>
+        <v>855</v>
       </c>
       <c r="N39" t="n">
-        <v>1110</v>
+        <v>414</v>
       </c>
       <c r="O39" t="n">
-        <v>3930</v>
+        <v>287</v>
       </c>
       <c r="P39" t="n">
-        <v>3930</v>
+        <v>-177</v>
       </c>
       <c r="Q39" t="n">
-        <v>3930</v>
+        <v>93</v>
       </c>
       <c r="R39" t="n">
-        <v>385</v>
+        <v>924</v>
       </c>
       <c r="S39" t="n">
-        <v>385</v>
+        <v>-567</v>
       </c>
       <c r="T39" t="n">
-        <v>385</v>
+        <v>-469</v>
+      </c>
+      <c r="U39" t="n">
+        <v>293</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) on Extinguishment of Debt</t>
+          <t>Effect of Exchange Rate on Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="D40" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F40" t="n">
-        <v>260</v>
+        <v>2</v>
       </c>
       <c r="G40" t="n">
-        <v>260</v>
+        <v>1</v>
       </c>
       <c r="H40" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
       </c>
       <c r="O40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
       </c>
       <c r="S40" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="T40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="U40" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>Asset Impairment Charges Including Equity Method Investments</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Period Increase (Decrease), Including Exchange Rate Effect</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>-4619</v>
       </c>
       <c r="C41" t="n">
-        <v>0</v>
+        <v>-4587</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>-88</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>-530</v>
       </c>
       <c r="F41" t="n">
-        <v>15</v>
+        <v>265</v>
       </c>
       <c r="G41" t="n">
-        <v>15</v>
+        <v>477</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>431</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>-115</v>
       </c>
       <c r="J41" t="n">
-        <v>0</v>
+        <v>-1503</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>-1365</v>
       </c>
       <c r="L41" t="n">
-        <v>198</v>
+        <v>-1409</v>
       </c>
       <c r="M41" t="n">
-        <v>155</v>
+        <v>2403</v>
       </c>
       <c r="N41" t="n">
-        <v>0</v>
+        <v>3484</v>
       </c>
       <c r="O41" t="n">
-        <v>306</v>
+        <v>1886</v>
       </c>
       <c r="P41" t="n">
-        <v>306</v>
+        <v>-1909</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>-3021</v>
       </c>
       <c r="R41" t="n">
-        <v>47</v>
+        <v>-3356</v>
       </c>
       <c r="S41" t="n">
-        <v>18</v>
+        <v>333</v>
       </c>
       <c r="T41" t="n">
-        <v>18</v>
+        <v>77</v>
+      </c>
+      <c r="U41" t="n">
+        <v>433</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>Income (Loss) from Equity Method Investments, Net of Dividends or Distributions</t>
+          <t>Cash, Cash Equivalents, Restricted Cash and Restricted Cash Equivalents, Including Disposal Group and Discontinued Operations</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0</v>
+        <v>4998</v>
       </c>
       <c r="C42" t="n">
-        <v>-2</v>
+        <v>4998</v>
       </c>
       <c r="D42" t="n">
-        <v>-1</v>
+        <v>1173</v>
       </c>
       <c r="E42" t="n">
-        <v>-1</v>
+        <v>1173</v>
       </c>
       <c r="F42" t="n">
-        <v>-6</v>
+        <v>1173</v>
       </c>
       <c r="G42" t="n">
-        <v>-4</v>
+        <v>649</v>
       </c>
       <c r="H42" t="n">
-        <v>-2</v>
+        <v>649</v>
       </c>
       <c r="I42" t="n">
-        <v>-16</v>
+        <v>649</v>
       </c>
       <c r="J42" t="n">
-        <v>-9</v>
+        <v>2178</v>
       </c>
       <c r="K42" t="n">
-        <v>-5</v>
+        <v>2178</v>
       </c>
       <c r="L42" t="n">
-        <v>7</v>
+        <v>2178</v>
       </c>
       <c r="M42" t="n">
-        <v>16</v>
+        <v>1110</v>
       </c>
       <c r="N42" t="n">
-        <v>18</v>
+        <v>1110</v>
       </c>
       <c r="O42" t="n">
-        <v>8</v>
+        <v>1110</v>
       </c>
       <c r="P42" t="n">
-        <v>14</v>
+        <v>3930</v>
       </c>
       <c r="Q42" t="n">
-        <v>17</v>
+        <v>3930</v>
       </c>
       <c r="R42" t="n">
-        <v>6</v>
+        <v>3930</v>
       </c>
       <c r="S42" t="n">
-        <v>7</v>
+        <v>385</v>
       </c>
       <c r="T42" t="n">
-        <v>16</v>
+        <v>385</v>
+      </c>
+      <c r="U42" t="n">
+        <v>385</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Payments for (Proceeds from) Hedge, Financing Activities</t>
+          <t>Asset Impairment Charges Including Equity Method Investments</t>
         </is>
       </c>
       <c r="B43" t="n">
         <v>0</v>
       </c>
       <c r="C43" t="n">
-        <v>-292</v>
+        <v>0</v>
       </c>
       <c r="D43" t="n">
         <v>0</v>
@@ -7767,10 +8109,10 @@
         <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="I43" t="n">
         <v>0</v>
@@ -7785,34 +8127,37 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>0</v>
+        <v>198</v>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>155</v>
       </c>
       <c r="O43" t="n">
         <v>0</v>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>306</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
       <c r="S43" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="T43" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="U43" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Payment for Debt Extinguishment or Debt Prepayment Cost</t>
+          <t>Income (Loss) from Equity Method Investments, Net of Dividends or Distributions</t>
         </is>
       </c>
       <c r="B44" t="n">
@@ -7822,61 +8167,64 @@
         <v>0</v>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="F44" t="n">
-        <v>-258</v>
+        <v>-1</v>
       </c>
       <c r="G44" t="n">
-        <v>-257</v>
+        <v>-6</v>
       </c>
       <c r="H44" t="n">
-        <v>-58</v>
+        <v>-4</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>-9</v>
       </c>
       <c r="L44" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N44" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="O44" t="n">
-        <v>-48</v>
+        <v>18</v>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="T44" t="n">
-        <v>0</v>
+        <v>7</v>
+      </c>
+      <c r="U44" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Gain (Loss) On Accretion Of Asset Retirement Obligations</t>
+          <t>Payments for (Proceeds from) Hedge, Financing Activities</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -7886,61 +8234,64 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>20</v>
+        <v>-292</v>
       </c>
       <c r="E45" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
-        <v>11</v>
+        <v>0</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Other Productive Assets</t>
+          <t>Gain (Loss) On Accretion Of Asset Retirement Obligations</t>
         </is>
       </c>
       <c r="B46" t="n">
@@ -7950,61 +8301,64 @@
         <v>0</v>
       </c>
       <c r="D46" t="n">
-        <v>-586</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
-        <v>-20</v>
+        <v>20</v>
       </c>
       <c r="F46" t="n">
-        <v>-33</v>
+        <v>-10</v>
       </c>
       <c r="G46" t="n">
-        <v>-32</v>
+        <v>29</v>
       </c>
       <c r="H46" t="n">
-        <v>-22</v>
+        <v>3</v>
       </c>
       <c r="I46" t="n">
-        <v>-2502</v>
+        <v>4</v>
       </c>
       <c r="J46" t="n">
-        <v>-2498</v>
+        <v>14</v>
       </c>
       <c r="K46" t="n">
-        <v>-2492</v>
+        <v>5</v>
       </c>
       <c r="L46" t="n">
-        <v>-60</v>
+        <v>6</v>
       </c>
       <c r="M46" t="n">
-        <v>-53</v>
+        <v>20</v>
       </c>
       <c r="N46" t="n">
-        <v>-26</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>-3534</v>
+        <v>7</v>
       </c>
       <c r="P46" t="n">
-        <v>-3521</v>
+        <v>21</v>
       </c>
       <c r="Q46" t="n">
-        <v>-3482</v>
+        <v>14</v>
       </c>
       <c r="R46" t="n">
-        <v>-277</v>
+        <v>3</v>
       </c>
       <c r="S46" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>18</v>
+      </c>
+      <c r="U46" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Amortization of Power Contracts Emission Credits</t>
+          <t>Payments to Acquire Other Productive Assets</t>
         </is>
       </c>
       <c r="B47" t="n">
@@ -8017,58 +8371,61 @@
         <v>0</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-586</v>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>-20</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>-33</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>-32</v>
       </c>
       <c r="I47" t="n">
-        <v>42</v>
+        <v>-22</v>
       </c>
       <c r="J47" t="n">
-        <v>26</v>
+        <v>-2502</v>
       </c>
       <c r="K47" t="n">
-        <v>13</v>
+        <v>-2498</v>
       </c>
       <c r="L47" t="n">
-        <v>42</v>
+        <v>-2492</v>
       </c>
       <c r="M47" t="n">
-        <v>28</v>
+        <v>-60</v>
       </c>
       <c r="N47" t="n">
-        <v>14</v>
+        <v>-53</v>
       </c>
       <c r="O47" t="n">
-        <v>39</v>
+        <v>-26</v>
       </c>
       <c r="P47" t="n">
-        <v>25</v>
+        <v>-3534</v>
       </c>
       <c r="Q47" t="n">
-        <v>13</v>
+        <v>-3521</v>
       </c>
       <c r="R47" t="n">
-        <v>40</v>
+        <v>-3482</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>-277</v>
       </c>
       <c r="T47" t="n">
-        <v>13</v>
+        <v>0</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Changes In Nuclear Decommissioning Trust Liability</t>
+          <t>Amortization of Power Contracts Emission Credits</t>
         </is>
       </c>
       <c r="B48" t="n">
@@ -8093,46 +8450,49 @@
         <v>0</v>
       </c>
       <c r="I48" t="n">
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="J48" t="n">
-        <v>2</v>
+        <v>42</v>
       </c>
       <c r="K48" t="n">
-        <v>-16</v>
+        <v>26</v>
       </c>
       <c r="L48" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="M48" t="n">
-        <v>-5</v>
+        <v>42</v>
       </c>
       <c r="N48" t="n">
-        <v>-7</v>
+        <v>28</v>
       </c>
       <c r="O48" t="n">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="P48" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="Q48" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="R48" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="S48" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="T48" t="n">
-        <v>8</v>
+        <v>25</v>
+      </c>
+      <c r="U48" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
+          <t>Changes In Nuclear Decommissioning Trust Liability</t>
         </is>
       </c>
       <c r="B49" t="n">
@@ -8157,46 +8517,49 @@
         <v>0</v>
       </c>
       <c r="I49" t="n">
-        <v>-293</v>
+        <v>0</v>
       </c>
       <c r="J49" t="n">
-        <v>-185</v>
+        <v>-4</v>
       </c>
       <c r="K49" t="n">
-        <v>-87</v>
+        <v>2</v>
       </c>
       <c r="L49" t="n">
-        <v>-361</v>
+        <v>-16</v>
       </c>
       <c r="M49" t="n">
-        <v>-271</v>
+        <v>2</v>
       </c>
       <c r="N49" t="n">
-        <v>-151</v>
+        <v>-5</v>
       </c>
       <c r="O49" t="n">
-        <v>-460</v>
+        <v>-7</v>
       </c>
       <c r="P49" t="n">
-        <v>-253</v>
+        <v>38</v>
       </c>
       <c r="Q49" t="n">
-        <v>-129</v>
+        <v>30</v>
       </c>
       <c r="R49" t="n">
-        <v>-360</v>
+        <v>15</v>
       </c>
       <c r="S49" t="n">
-        <v>-257</v>
+        <v>39</v>
       </c>
       <c r="T49" t="n">
-        <v>-121</v>
+        <v>36</v>
+      </c>
+      <c r="U49" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
+          <t>Payments to Acquire Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B50" t="n">
@@ -8221,46 +8584,49 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>180</v>
+        <v>-293</v>
       </c>
       <c r="K50" t="n">
-        <v>99</v>
+        <v>-185</v>
       </c>
       <c r="L50" t="n">
-        <v>363</v>
+        <v>-87</v>
       </c>
       <c r="M50" t="n">
-        <v>278</v>
+        <v>-361</v>
       </c>
       <c r="N50" t="n">
-        <v>161</v>
+        <v>-271</v>
       </c>
       <c r="O50" t="n">
-        <v>424</v>
+        <v>-151</v>
       </c>
       <c r="P50" t="n">
-        <v>226</v>
+        <v>-460</v>
       </c>
       <c r="Q50" t="n">
-        <v>118</v>
+        <v>-253</v>
       </c>
       <c r="R50" t="n">
-        <v>318</v>
+        <v>-129</v>
       </c>
       <c r="S50" t="n">
-        <v>220</v>
+        <v>-360</v>
       </c>
       <c r="T50" t="n">
-        <v>112</v>
+        <v>-257</v>
+      </c>
+      <c r="U50" t="n">
+        <v>-121</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Preferred Stock and Preference Stock</t>
+          <t>Proceeds from Sale of Debt Securities, Available-for-sale</t>
         </is>
       </c>
       <c r="B51" t="n">
@@ -8285,46 +8651,49 @@
         <v>0</v>
       </c>
       <c r="I51" t="n">
-        <v>635</v>
+        <v>0</v>
       </c>
       <c r="J51" t="n">
-        <v>635</v>
+        <v>280</v>
       </c>
       <c r="K51" t="n">
-        <v>636</v>
+        <v>180</v>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>99</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>363</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>278</v>
       </c>
       <c r="O51" t="n">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>424</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>226</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>118</v>
       </c>
       <c r="S51" t="n">
-        <v>0</v>
+        <v>318</v>
       </c>
       <c r="T51" t="n">
-        <v>0</v>
+        <v>220</v>
+      </c>
+      <c r="U51" t="n">
+        <v>112</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Repayments of) Lines of Credit</t>
+          <t>Proceeds from Issuance of Preferred Stock and Preference Stock</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -8349,16 +8718,16 @@
         <v>0</v>
       </c>
       <c r="I52" t="n">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="J52" t="n">
-        <v>700</v>
+        <v>635</v>
       </c>
       <c r="K52" t="n">
-        <v>950</v>
+        <v>635</v>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
+        <v>636</v>
       </c>
       <c r="M52" t="n">
         <v>0</v>
@@ -8370,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="P52" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
@@ -8382,13 +8751,16 @@
         <v>0</v>
       </c>
       <c r="T52" t="n">
+        <v>0</v>
+      </c>
+      <c r="U52" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from Issuance of Common Stock</t>
+          <t>Proceeds from (Repayments of) Lines of Credit</t>
         </is>
       </c>
       <c r="B53" t="n">
@@ -8416,13 +8788,13 @@
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>300</v>
       </c>
       <c r="K53" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
+        <v>950</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -8431,28 +8803,31 @@
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>75</v>
       </c>
       <c r="R53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53" t="n">
+        <v>0</v>
+      </c>
+      <c r="U53" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>Gains (Losses) On Extinguishment Of Debt Non Cash Portion</t>
+          <t>Proceeds from Issuance of Common Stock</t>
         </is>
       </c>
       <c r="B54" t="n">
@@ -8495,13 +8870,13 @@
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R54" t="n">
         <v>1</v>
@@ -8510,13 +8885,16 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>-1</v>
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>Investments In Proceeds From Sales Of Unconsolidated Affiliates</t>
+          <t>Gains (Losses) On Extinguishment Of Debt Non Cash Portion</t>
         </is>
       </c>
       <c r="B55" t="n">
@@ -8562,25 +8940,28 @@
         <v>0</v>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>57</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments for) Other Financing Activities</t>
+          <t>Investments In Proceeds From Sales Of Unconsolidated Affiliates</t>
         </is>
       </c>
       <c r="B56" t="n">
@@ -8623,28 +9004,31 @@
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>396</v>
+        <v>0</v>
       </c>
       <c r="P56" t="n">
-        <v>191</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>-6</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>-5</v>
+        <v>2</v>
       </c>
       <c r="T56" t="n">
-        <v>-3</v>
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>Proceeds from (Payments to) Noncontrolling Interests</t>
+          <t>Proceeds from (Payments for) Other Financing Activities</t>
         </is>
       </c>
       <c r="B57" t="n">
@@ -8690,82 +9074,155 @@
         <v>0</v>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>396</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="R57" t="n">
-        <v>-2</v>
+        <v>190</v>
       </c>
       <c r="S57" t="n">
-        <v>-2</v>
+        <v>-6</v>
       </c>
       <c r="T57" t="n">
-        <v>-2</v>
+        <v>-5</v>
+      </c>
+      <c r="U57" t="n">
+        <v>-3</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>Proceeds from (Payments to) Noncontrolling Interests</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" t="n">
+        <v>0</v>
+      </c>
+      <c r="P58" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>0</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0</v>
+      </c>
+      <c r="S58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="T58" t="n">
+        <v>-2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
           <t>Amortization Of Intangibles And Out Of Market Contracts</t>
         </is>
       </c>
-      <c r="B58" t="n">
-        <v>0</v>
-      </c>
-      <c r="C58" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" t="n">
-        <v>0</v>
-      </c>
-      <c r="P58" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q58" t="n">
+      <c r="B59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
         <v>7</v>
       </c>
-      <c r="R58" t="n">
+      <c r="S59" t="n">
         <v>60</v>
       </c>
-      <c r="S58" t="n">
+      <c r="T59" t="n">
         <v>33</v>
       </c>
-      <c r="T58" t="n">
+      <c r="U59" t="n">
         <v>7</v>
       </c>
     </row>
